--- a/inventories/lci-lithium_brine_projects.xlsx
+++ b/inventories/lci-lithium_brine_projects.xlsx
@@ -31,7 +31,7 @@
     <t>code</t>
   </si>
   <si>
-    <t>da397efc1f2447649b1777522bd1a5fa</t>
+    <t>acdbdfa9c6f248388626239241a3834e</t>
   </si>
   <si>
     <t>location</t>
@@ -103,7 +103,7 @@
     <t>Water_Ang_Sal de los Angeles</t>
   </si>
   <si>
-    <t>6d06c0fda9f24f309d2c2292c654f965</t>
+    <t>bd37f297ac8e4e4a9a132824bac8991f</t>
   </si>
   <si>
     <t>AR</t>
@@ -148,7 +148,7 @@
     <t>Water_Ari_Salar de Arizaro</t>
   </si>
   <si>
-    <t>5803a098ab864810a6c0028aa3d61f8b</t>
+    <t>2fc24474f5144c6d99443f0d95fe880f</t>
   </si>
   <si>
     <t>Water_Ari</t>
@@ -169,7 +169,7 @@
     <t>Water_Ata_Salar de Atacama</t>
   </si>
   <si>
-    <t>19b8ef8df6b746ff80fde0d3079ea3c0</t>
+    <t>dde256e3537742ce87457db294a21356</t>
   </si>
   <si>
     <t>CL</t>
@@ -184,7 +184,7 @@
     <t>Water_Cau_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>770aebd8b0e047a0abef2927b899d0b4</t>
+    <t>c399f867ea2643d7981a78dc798826ec</t>
   </si>
   <si>
     <t>Water_Cau</t>
@@ -196,7 +196,7 @@
     <t>Water_Cent_Salar de Centenario</t>
   </si>
   <si>
-    <t>fa98e22be4064d2e97e725380fe52afc</t>
+    <t>1e6374ba3c5c428d8289bf11742992dd</t>
   </si>
   <si>
     <t>Water_Cent</t>
@@ -208,7 +208,7 @@
     <t>Water_Chaer_Chaerhan</t>
   </si>
   <si>
-    <t>1fead59339094229acf5bd50e1e8871f</t>
+    <t>fdca08c4737845d8b087a229cf575017</t>
   </si>
   <si>
     <t>CN-NWG</t>
@@ -223,7 +223,7 @@
     <t>Water_EaTai_East Taijinar</t>
   </si>
   <si>
-    <t>6d2b792e81254d32af86fa74e3d24e5f</t>
+    <t>c2c8cb50eec84fe98a5e4e679122b3d4</t>
   </si>
   <si>
     <t>Water_EaTai</t>
@@ -235,7 +235,7 @@
     <t>Water_Fen_Fenix</t>
   </si>
   <si>
-    <t>9a2a83e7e7604a518efc21880e1dc9a0</t>
+    <t>8802dd02857a4a6fb9c2fbdb7ae668bf</t>
   </si>
   <si>
     <t>Water_Fen</t>
@@ -247,7 +247,7 @@
     <t>Water_Hom_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>959942b50e3743419f15a3ac7ecc40cf</t>
+    <t>75bc7b32229548bab422adf5c517f265</t>
   </si>
   <si>
     <t>Water_Hom</t>
@@ -268,7 +268,7 @@
     <t>Water_Kach_Kachi</t>
   </si>
   <si>
-    <t>3d9e7fa0bdf343d0b36ec066d4fd8723</t>
+    <t>98d1bde5b0ae4cc6980a2d8000a5a6fc</t>
   </si>
   <si>
     <t>Water_Kach</t>
@@ -280,7 +280,7 @@
     <t>Water_Lak_Lakkor Tso</t>
   </si>
   <si>
-    <t>51ab63b69d3f44ceb0a2df662a0a4ac6</t>
+    <t>c877380258944ad49fa658480b385829</t>
   </si>
   <si>
     <t>Water_Lak</t>
@@ -292,7 +292,7 @@
     <t>Water_Mari_Maricunga</t>
   </si>
   <si>
-    <t>9c12205ff652410787c20e714bb74da3</t>
+    <t>07aefea2ff494b45b4f49c50424ff382</t>
   </si>
   <si>
     <t>Water_Mari</t>
@@ -304,7 +304,7 @@
     <t>Water_Ola_Salar de Olaroz</t>
   </si>
   <si>
-    <t>a923ff9d5e0745ac850ac27c8dee18b0</t>
+    <t>799e485afd8c499bb9fe6e61fd9af21c</t>
   </si>
   <si>
     <t>Water_Ola</t>
@@ -316,7 +316,7 @@
     <t>Water_Pas_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>23554922ddcd40a4a4995b2403af8519</t>
+    <t>857a62e760234c5695675a975ff6dd90</t>
   </si>
   <si>
     <t>Water_Pas</t>
@@ -331,7 +331,7 @@
     <t>Water_Poz_Pozuelos</t>
   </si>
   <si>
-    <t>5f94ae19560a4efd89c5eaf840aa458e</t>
+    <t>8375f89dadfa4bd59f92687675407bce</t>
   </si>
   <si>
     <t>Water_Poz</t>
@@ -346,7 +346,7 @@
     <t>Water_Rin_Salar del Rincon</t>
   </si>
   <si>
-    <t>b14c2b1d37ba4f06889d6a5332485517</t>
+    <t>b1c8756530f246f0bf4d8a235c47d1b7</t>
   </si>
   <si>
     <t>Water_Rin</t>
@@ -358,7 +358,7 @@
     <t>Water_Sil_Silver Peak</t>
   </si>
   <si>
-    <t>b1d7d90841ba41439b444113014041e3</t>
+    <t>4b94cdbadd3047fb92aed7f6237d1f3e</t>
   </si>
   <si>
     <t>US-WECC</t>
@@ -373,7 +373,7 @@
     <t>Water_Tol_Salar de Tolillar</t>
   </si>
   <si>
-    <t>6ea4cffaea2241e5bda7c53bd298c3b7</t>
+    <t>e2feabf3c8bb45e89a6137531199e2a4</t>
   </si>
   <si>
     <t>Water_Tol</t>
@@ -385,7 +385,7 @@
     <t>Water_TresQ_Tres Quebradas</t>
   </si>
   <si>
-    <t>b93984d87d7f47768ee90eadcc4728a7</t>
+    <t>69b9f40ce35c40bb8f171233d6b9adc1</t>
   </si>
   <si>
     <t>Water_TresQ</t>
@@ -397,7 +397,7 @@
     <t>Water_URG_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>989f8cfa679846749aab7fb8960a93a4</t>
+    <t>3ca2a61d9c1f4f4782d70a995e4108f2</t>
   </si>
   <si>
     <t>Water_URG</t>
@@ -412,7 +412,7 @@
     <t>Water_Uyu_Salar de Uyuni</t>
   </si>
   <si>
-    <t>7fab0f5d5ad24c4798d1dd7f56bb0ea5</t>
+    <t>5769d50474a6453f9a324341518d3483</t>
   </si>
   <si>
     <t>BO</t>
@@ -427,7 +427,7 @@
     <t>Water_Vid_Sal de Vida</t>
   </si>
   <si>
-    <t>dd2986e18b69490c999d05072c2a18ad</t>
+    <t>691236e863ed439794c3775067b9ae86</t>
   </si>
   <si>
     <t>Water_Vid</t>
@@ -439,7 +439,7 @@
     <t>Water_Yilip_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>13fa875833734599b8601742165ec1e3</t>
+    <t>1771a50a0ebc4621bd46c8b39a4547c8</t>
   </si>
   <si>
     <t>Water_Yilip</t>
@@ -451,7 +451,7 @@
     <t>Water_Zha_Zhabuye</t>
   </si>
   <si>
-    <t>fc2f3f30f14a4922a5d479b135da8b65</t>
+    <t>977815536732415ebe6110c1d29a9ed3</t>
   </si>
   <si>
     <t>Water_Zha</t>
@@ -463,7 +463,7 @@
     <t>df_B_removal_orgsolvent_Maricunga</t>
   </si>
   <si>
-    <t>aa0ee8c1b9a240a8b851e28f0cc51682</t>
+    <t>26533f4debd54e9ba7266142de0b43bb</t>
   </si>
   <si>
     <t>df_B_removal_orgsolvent</t>
@@ -511,7 +511,7 @@
     <t>df_B_removal_orgsolvent_Salar de Atacama</t>
   </si>
   <si>
-    <t>6421637ffe8f46f2bfe96e2757be53f7</t>
+    <t>ff13ebab75864f789d4482f80a19fff4</t>
   </si>
   <si>
     <t>df_transport_brine_Salar de Atacama</t>
@@ -523,7 +523,7 @@
     <t>df_B_removal_orgsolvent_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>9749fcc97b724d43b276395f075eace3</t>
+    <t>5a6c27e177024a44a97b3f6084f3edcf</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar de Cauchari-Olaroz</t>
@@ -532,19 +532,19 @@
     <t>df_B_removal_orgsolvent_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>2b700157bc50464daa5a9fbbce38204a</t>
+    <t>16ec05f83c8a4f2cb8206f949b408705</t>
   </si>
   <si>
     <t>df_B_removal_orgsolvent_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>7bc469ee3db54a06a5f371fccc88c3af</t>
+    <t>c1f3cc3f46694665bb89e88c8e14f739</t>
   </si>
   <si>
     <t>df_B_removal_orgsolvent_Tres Quebradas</t>
   </si>
   <si>
-    <t>959980a09f764fabb7f9686342cedafa</t>
+    <t>4e889a2d73d544e9b24737354b137478</t>
   </si>
   <si>
     <t>df_transport_brine_Tres Quebradas</t>
@@ -553,7 +553,7 @@
     <t>df_CaMg_removal_sodiumhydrox_Sal de Vida</t>
   </si>
   <si>
-    <t>3766393146b24b8bb21fa674a9008c81</t>
+    <t>b2212ea21ee0489c9bf521b0fa9530f5</t>
   </si>
   <si>
     <t>df_CaMg_removal_sodiumhydrox</t>
@@ -562,7 +562,7 @@
     <t>df_CaMg_removal_sodiumhydrox_Tres Quebradas</t>
   </si>
   <si>
-    <t>ef5f454cb68f4ef09d99fd65d7cad2b8</t>
+    <t>7653f77cb6e74c86b2fa4f96914e7e45</t>
   </si>
   <si>
     <t>df_centrifuge_purification_sodaash_Tres Quebradas</t>
@@ -586,7 +586,7 @@
     <t>df_CaMg_removal_sodiumhydrox_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>9734f99289bd48a897070f8bceb9e382</t>
+    <t>c3de3a4a05614b63a909e64eea707f90</t>
   </si>
   <si>
     <t>df_Li_adsorption_Upper Rhine Graben</t>
@@ -604,7 +604,7 @@
     <t>df_DLE_evaporation_ponds_Chaerhan</t>
   </si>
   <si>
-    <t>cbc77ddce405476a8e77f8a0912d581b</t>
+    <t>5cd19572eb8c426f9528fe76aeb84c8a</t>
   </si>
   <si>
     <t>df_DLE_evaporation_ponds</t>
@@ -643,7 +643,7 @@
     <t>df_DLE_evaporation_ponds_Fenix</t>
   </si>
   <si>
-    <t>bb28d893b95e4581b0c08df8d617d39c</t>
+    <t>0395303f47da48208fddd12b3e9668d5</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Fenix</t>
@@ -661,7 +661,7 @@
     <t>df_DLE_evaporation_ponds_Kachi</t>
   </si>
   <si>
-    <t>85baecbed9e44f6dafc4e029a15649dc</t>
+    <t>10c391cf16c9441fa2575308110ce5f6</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Kachi</t>
@@ -676,7 +676,7 @@
     <t>df_DLE_evaporation_ponds_Lakkor Tso</t>
   </si>
   <si>
-    <t>acfe406457a746eb9f6c5c0c7f748534</t>
+    <t>1bbfb424ea404393ac0c31bc3c632629</t>
   </si>
   <si>
     <t>df_reverse_osmosis_Lakkor Tso</t>
@@ -691,13 +691,13 @@
     <t>df_DLE_evaporation_ponds_Pozuelos</t>
   </si>
   <si>
-    <t>4cf8a3712dba4f0596f9d64b0dccc5b1</t>
+    <t>317bdb7d23ee49c995107c7f6b450857</t>
   </si>
   <si>
     <t>df_DLE_evaporation_ponds_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>0b6ec68fc8ec4394b731d108e534912b</t>
+    <t>ad01df56814848f392a3812a35a6e6b7</t>
   </si>
   <si>
     <t>df_reverse_osmosis_Qinghai Yiliping</t>
@@ -712,7 +712,7 @@
     <t>df_DLE_evaporation_ponds_Sal de los Angeles</t>
   </si>
   <si>
-    <t>beb995d344d94cb4be66d6b7ca62131d</t>
+    <t>b7d2e257dec6499298fca6e15acca544</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Sal de los Angeles</t>
@@ -727,13 +727,13 @@
     <t>df_DLE_evaporation_ponds_Salar de Arizaro</t>
   </si>
   <si>
-    <t>168054f910924fa5899dd971d02fe9c4</t>
+    <t>74102006ad4f45bda0b4fc1dcaef4a79</t>
   </si>
   <si>
     <t>df_DLE_evaporation_ponds_Salar de Centenario</t>
   </si>
   <si>
-    <t>e34a9dcd78e24949a6c372ed9e900e1f</t>
+    <t>b8b01d8315b746e6993057fc4e4c98f6</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Salar de Centenario</t>
@@ -748,13 +748,13 @@
     <t>df_DLE_evaporation_ponds_Salar de Tolillar</t>
   </si>
   <si>
-    <t>ede191b14e314fcb9e907d3a89bc7d65</t>
+    <t>058a65fbebbb409eba399e6df712c246</t>
   </si>
   <si>
     <t>df_DLE_evaporation_ponds_Salar de Uyuni</t>
   </si>
   <si>
-    <t>87fd1a29bbcf46a18cfe9c4fc75c64d9</t>
+    <t>bfaac69336b1417d90ff357097c1ab0d</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Salar de Uyuni</t>
@@ -769,7 +769,7 @@
     <t>df_DLE_evaporation_ponds_Salar del Rincon</t>
   </si>
   <si>
-    <t>0a3cd0a2ea8b47f0aea803d3e445ab7b</t>
+    <t>4f4b3592927841379927231683fe2476</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Salar del Rincon</t>
@@ -784,7 +784,7 @@
     <t>df_Li_adsorption_Chaerhan</t>
   </si>
   <si>
-    <t>eefac91f50764f71a88ae5017dc1c088</t>
+    <t>31bb8e079348474c8d9617c0a0f3388b</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Chaerhan</t>
@@ -799,7 +799,7 @@
     <t>df_Li_adsorption_East Taijinar</t>
   </si>
   <si>
-    <t>5d7845d6779d47cbac2bd83d620b0c29</t>
+    <t>508fe9b8a13a476280ab962c633704fa</t>
   </si>
   <si>
     <t>df_acidification_East Taijinar</t>
@@ -811,7 +811,7 @@
     <t>df_Li_adsorption_Fenix</t>
   </si>
   <si>
-    <t>cb7c8660d57443a4838c3ba1392ffcea</t>
+    <t>e41f720ed2fd47db8e6775e0fac12500</t>
   </si>
   <si>
     <t>df_acidification_Fenix</t>
@@ -820,7 +820,7 @@
     <t>df_Li_adsorption_Kachi</t>
   </si>
   <si>
-    <t>d462c21af8864a4397b2ecc418cd91d5</t>
+    <t>9b80b6053c7c4244ac07691852fd90ae</t>
   </si>
   <si>
     <t>df_acidification_Kachi</t>
@@ -829,7 +829,7 @@
     <t>df_Li_adsorption_Lakkor Tso</t>
   </si>
   <si>
-    <t>b766fd4c701c47db9221a9f800caed43</t>
+    <t>766f1685e1c04d1b9495151a983c1e56</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Lakkor Tso</t>
@@ -838,13 +838,13 @@
     <t>df_Li_adsorption_Pozuelos</t>
   </si>
   <si>
-    <t>b4b6b64791034bc0ab1e4f4e5166e1dc</t>
+    <t>53ef7b6e2bb145aaa2fd847815a89c12</t>
   </si>
   <si>
     <t>df_Li_adsorption_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>46a6a86adb97465dbfe4301477fed8a3</t>
+    <t>feb276911cc94136a83895114bbf1769</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Qinghai Yiliping</t>
@@ -853,7 +853,7 @@
     <t>df_Li_adsorption_Sal de los Angeles</t>
   </si>
   <si>
-    <t>341a2b2d94f24ef78efcdce29b01ee1b</t>
+    <t>f09cd5d6f6654bb6a4106e11f19f8d54</t>
   </si>
   <si>
     <t>df_acidification_Sal de los Angeles</t>
@@ -862,13 +862,13 @@
     <t>df_Li_adsorption_Salar de Arizaro</t>
   </si>
   <si>
-    <t>3e25b0c46bf04b1d9f24c5f19c8eff96</t>
+    <t>f717f1aa29194cee99b56126abe17a3c</t>
   </si>
   <si>
     <t>df_Li_adsorption_Salar de Centenario</t>
   </si>
   <si>
-    <t>f3cd19c4f2d44848b4ee252afca2d75a</t>
+    <t>9cca810a6f8a4193af27763d808a0d0c</t>
   </si>
   <si>
     <t>df_acidification_Salar de Centenario</t>
@@ -877,13 +877,13 @@
     <t>df_Li_adsorption_Salar de Tolillar</t>
   </si>
   <si>
-    <t>1e3b631044ca4da1b5c8cb837447df45</t>
+    <t>598bb7b42d844aaaa98f6920b2b05ba8</t>
   </si>
   <si>
     <t>df_Li_adsorption_Salar de Uyuni</t>
   </si>
   <si>
-    <t>748d5fd96aa54cacad72a312124f10d5</t>
+    <t>52d54657532b47b7bc7b383ced6e2dc6</t>
   </si>
   <si>
     <t>df_acidification_Salar de Uyuni</t>
@@ -892,7 +892,7 @@
     <t>df_Li_adsorption_Salar del Rincon</t>
   </si>
   <si>
-    <t>ed98d0cba1a847fead73f0e93a166c89</t>
+    <t>06d4cd9676b145caaa59bc3b5ff68d54</t>
   </si>
   <si>
     <t>df_acidification_Salar del Rincon</t>
@@ -904,7 +904,7 @@
     <t>heat, central or small-scale, other than natural gas</t>
   </si>
   <si>
-    <t>4742a46b7eac4bc28ca9099cf4dc758a</t>
+    <t>3140f99addc544598c65d1ee5ac50597</t>
   </si>
   <si>
     <t>df_acidification_Upper Rhine Graben</t>
@@ -913,7 +913,7 @@
     <t>df_Liprec_BG_Chaerhan</t>
   </si>
   <si>
-    <t>02ff18d837f842128463cad8e40b8bed</t>
+    <t>1b646b96b9da4f1fa985d16c9012e3a0</t>
   </si>
   <si>
     <t>df_Liprec_BG</t>
@@ -928,7 +928,7 @@
     <t>df_Liprec_BG_East Taijinar</t>
   </si>
   <si>
-    <t>7a660a63992c41198ce3599302731cac</t>
+    <t>fa1f01558e704489a178e4d1a4272666</t>
   </si>
   <si>
     <t>df_dissolution_East Taijinar</t>
@@ -937,7 +937,7 @@
     <t>df_Liprec_BG_Fenix</t>
   </si>
   <si>
-    <t>c426549139204e799fa1810969210e34</t>
+    <t>bb2c88e0fb524d1db38596f996f39947</t>
   </si>
   <si>
     <t>df_dissolution_Fenix</t>
@@ -946,7 +946,7 @@
     <t>df_Liprec_BG_Kachi</t>
   </si>
   <si>
-    <t>37b4cb8074e44837ba2bddc76bbc069c</t>
+    <t>8d9e7d370fbe46f1aa541d113c12ab9f</t>
   </si>
   <si>
     <t>df_dissolution_Kachi</t>
@@ -955,7 +955,7 @@
     <t>df_Liprec_BG_Lakkor Tso</t>
   </si>
   <si>
-    <t>2c43259f255f40f0935ee24df09c9e81</t>
+    <t>3de53654d8054e5397d2a9c072630873</t>
   </si>
   <si>
     <t>df_dissolution_Lakkor Tso</t>
@@ -964,7 +964,7 @@
     <t>df_Liprec_BG_Maricunga</t>
   </si>
   <si>
-    <t>430e3966a4264c3b94492306258b6466</t>
+    <t>f19b91f9912c4018bd6b79508dc2b2c2</t>
   </si>
   <si>
     <t>df_dissolution_Maricunga</t>
@@ -979,13 +979,13 @@
     <t>df_Liprec_BG_Pozuelos</t>
   </si>
   <si>
-    <t>601bbf4ffee14888b44c2157920879ab</t>
+    <t>0927aa46f99f4109b37548833e9fde0c</t>
   </si>
   <si>
     <t>df_Liprec_BG_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>56d0a180899b4329bf60793a9d3b80d7</t>
+    <t>5be76fee429f4f8a85e7d42a41001ece</t>
   </si>
   <si>
     <t>df_dissolution_Qinghai Yiliping</t>
@@ -994,13 +994,13 @@
     <t>df_Liprec_BG_Sal de Vida</t>
   </si>
   <si>
-    <t>c887b3f20ba04c2f8b426b984f3bd3be</t>
+    <t>ce8d3bf7db2f4b42ab7d25fb0cc18b77</t>
   </si>
   <si>
     <t>df_Liprec_BG_Sal de los Angeles</t>
   </si>
   <si>
-    <t>a6ae0b6382bb4617ad95d0ff3dfc56e8</t>
+    <t>bdf8a9a7ae534b0482266b47c4a94e02</t>
   </si>
   <si>
     <t>df_dissolution_Sal de los Angeles</t>
@@ -1009,13 +1009,13 @@
     <t>df_Liprec_BG_Salar de Arizaro</t>
   </si>
   <si>
-    <t>79fdfbbbebe94b08b902e3f1c956fea7</t>
+    <t>5de08f5b38a6459ea7519062bddcdfd3</t>
   </si>
   <si>
     <t>df_Liprec_BG_Salar de Atacama</t>
   </si>
   <si>
-    <t>2cdef0bfa0ee45e49a87f9cbe98c7df8</t>
+    <t>8bac6b7e37bb4175a8baa5eff4e83eff</t>
   </si>
   <si>
     <t>df_dissolution_Salar de Atacama</t>
@@ -1024,7 +1024,7 @@
     <t>df_Liprec_BG_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>cc830f6ab5b54ac0ba99938c7b391ee7</t>
+    <t>5393ef22f42e42139937b9f953d53aaa</t>
   </si>
   <si>
     <t>df_dissolution_Salar de Cauchari-Olaroz</t>
@@ -1033,7 +1033,7 @@
     <t>df_Liprec_BG_Salar de Centenario</t>
   </si>
   <si>
-    <t>eef4b805883e41d8a02a2bfa5750921d</t>
+    <t>8b19245d31be42f298cf74547b1321ea</t>
   </si>
   <si>
     <t>df_dissolution_Salar de Centenario</t>
@@ -1042,7 +1042,7 @@
     <t>df_Liprec_BG_Salar de Olaroz</t>
   </si>
   <si>
-    <t>a72c07a10b904ec8978a75f9b17f905b</t>
+    <t>dd85fab69e6b4cd09581666c87df8089</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Salar de Olaroz</t>
@@ -1051,19 +1051,19 @@
     <t>df_Liprec_BG_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>f2afbef650954c7392142164812de9c6</t>
+    <t>141c499b91c240b0aeb51c672c23b9e4</t>
   </si>
   <si>
     <t>df_Liprec_BG_Salar de Tolillar</t>
   </si>
   <si>
-    <t>48d247361ede494dbe972fe8be9c4da0</t>
+    <t>8758c60fda984036b5294f99741d244f</t>
   </si>
   <si>
     <t>df_Liprec_BG_Salar de Uyuni</t>
   </si>
   <si>
-    <t>7a4045148e964eaf819afbf5146591a3</t>
+    <t>d8499269ecc2497c8645ee3b5c5c37f5</t>
   </si>
   <si>
     <t>df_dissolution_Salar de Uyuni</t>
@@ -1072,13 +1072,13 @@
     <t>df_Liprec_BG_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>782df7cd99894e7a95e35133f44968b4</t>
+    <t>c906cb80aff84723b55738294fade64b</t>
   </si>
   <si>
     <t>df_Liprec_BG_Salar del Rincon</t>
   </si>
   <si>
-    <t>7727a46795a34eeda18fc26c51a915cc</t>
+    <t>991c65db7c0d4aa5b17fb63562497be4</t>
   </si>
   <si>
     <t>df_dissolution_Salar del Rincon</t>
@@ -1087,7 +1087,7 @@
     <t>df_Liprec_BG_Silver Peak</t>
   </si>
   <si>
-    <t>e8d78ef189e5464a899feef7c49a4de5</t>
+    <t>f20a89fd7fd64cdb9f09821ee9e8fe49</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Silver Peak</t>
@@ -1099,7 +1099,7 @@
     <t>df_Liprec_BG_Tres Quebradas</t>
   </si>
   <si>
-    <t>ec3841a607c442eca0ba29cfc41c815a</t>
+    <t>1d1b27ca62734356a4a3ab584f6527f1</t>
   </si>
   <si>
     <t>df_dissolution_Tres Quebradas</t>
@@ -1108,7 +1108,7 @@
     <t>df_Liprec_BG_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>75a029e0744a43eea4ee19d538791e04</t>
+    <t>df86831f891747d29ba711197595a9c5</t>
   </si>
   <si>
     <t>df_dissolution_Upper Rhine Graben</t>
@@ -1117,7 +1117,7 @@
     <t>df_Liprec_BG_Zhabuye</t>
   </si>
   <si>
-    <t>e3473b60567d4384b7a53867085a3459</t>
+    <t>f1f511b4c32f4661af48dd17f28e5049</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Zhabuye</t>
@@ -1126,7 +1126,7 @@
     <t>df_Liprec_TG_Chaerhan</t>
   </si>
   <si>
-    <t>1ee835cbeb264b558dd3d3c58cae880d</t>
+    <t>3973a160155a4a77befd4c6878c4b259</t>
   </si>
   <si>
     <t>df_Liprec_TG</t>
@@ -1135,7 +1135,7 @@
     <t>df_Liprec_TG_East Taijinar</t>
   </si>
   <si>
-    <t>02270a1050e24560846271b5d20d0bc4</t>
+    <t>719cb2518ae943c78f5306dd908966d3</t>
   </si>
   <si>
     <t>df_reverse_osmosis_East Taijinar</t>
@@ -1144,25 +1144,25 @@
     <t>df_Liprec_TG_Fenix</t>
   </si>
   <si>
-    <t>1a707954dddb4dda84613f0dfeedc6e3</t>
+    <t>c0c634dd6c334b93883dff42a35375ab</t>
   </si>
   <si>
     <t>df_Liprec_TG_Kachi</t>
   </si>
   <si>
-    <t>557fdd1c04a6468eb01b52ddf001cba5</t>
+    <t>112b6077a7784ad1a6051e3ec0dda4cb</t>
   </si>
   <si>
     <t>df_Liprec_TG_Lakkor Tso</t>
   </si>
   <si>
-    <t>2adc8c84120842abaeadf922a5bf24d7</t>
+    <t>0101e3b22174473989ed1830a051cf0f</t>
   </si>
   <si>
     <t>df_Liprec_TG_Maricunga</t>
   </si>
   <si>
-    <t>9ee8216a03ca402d8f9a7833cdb6e0e4</t>
+    <t>dd6d4704845d4a9a8dd92f1a09ac2d0e</t>
   </si>
   <si>
     <t>df_ion_exchange_H_Maricunga</t>
@@ -1174,37 +1174,37 @@
     <t>df_Liprec_TG_Pozuelos</t>
   </si>
   <si>
-    <t>480ad3a36ecf49bba7755a3630f3015a</t>
+    <t>251c44755b6943afa0acf4301d9aa4bc</t>
   </si>
   <si>
     <t>df_Liprec_TG_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>dda17c7fe5dc4206a811f2c1bd3c9460</t>
+    <t>9b085036bde445d4b136d9d481c51603</t>
   </si>
   <si>
     <t>df_Liprec_TG_Sal de Vida</t>
   </si>
   <si>
-    <t>24ae3fd308754356a912f60b20464825</t>
+    <t>df66f217498e4ae88fcc0f6be85a8e89</t>
   </si>
   <si>
     <t>df_Liprec_TG_Sal de los Angeles</t>
   </si>
   <si>
-    <t>d3e97a0dc35246bcb40a6e83d4984efb</t>
+    <t>a6f2353c78714b49b75cbeaedc7025b9</t>
   </si>
   <si>
     <t>df_Liprec_TG_Salar de Arizaro</t>
   </si>
   <si>
-    <t>b0eb6e03bc144b25a248f84a2e0064b4</t>
+    <t>0a263af138c5468683c66ad0f906f354</t>
   </si>
   <si>
     <t>df_Liprec_TG_Salar de Atacama</t>
   </si>
   <si>
-    <t>fe1154efc3194c8b8907fd32a332c5a5</t>
+    <t>b0b10694fa2c464c8cb529252d96f250</t>
   </si>
   <si>
     <t>df_centrifuge_purification_quicklime_Salar de Atacama</t>
@@ -1216,7 +1216,7 @@
     <t>df_Liprec_TG_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>4b6fd569c8c9470bbf3431d6481e323c</t>
+    <t>a573fb68e9b446a0bdac46f0bcc4193b</t>
   </si>
   <si>
     <t>df_triple_evaporator_Salar de Cauchari-Olaroz</t>
@@ -1228,13 +1228,13 @@
     <t>df_Liprec_TG_Salar de Centenario</t>
   </si>
   <si>
-    <t>cf3122d203254e1992eba0e3cdb5d86a</t>
+    <t>2d0679f7d20045368414a2e7207d3c85</t>
   </si>
   <si>
     <t>df_Liprec_TG_Salar de Olaroz</t>
   </si>
   <si>
-    <t>8f4a875fa23340cd9082e1c7bba947ed</t>
+    <t>3ee9744873e84e7a856f963cfd7cddf2</t>
   </si>
   <si>
     <t>df_centrifuge_general_1_Salar de Olaroz</t>
@@ -1246,37 +1246,37 @@
     <t>df_Liprec_TG_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>ba63bf7d47ca4b5bb44a128e713efe85</t>
+    <t>0008d46cc4fb43bc936f507108c7700f</t>
   </si>
   <si>
     <t>df_Liprec_TG_Salar de Tolillar</t>
   </si>
   <si>
-    <t>c248cfe3c7694bb380cb113f9d4ebb4e</t>
+    <t>b052f17b6af44ed5a4182f3855edece7</t>
   </si>
   <si>
     <t>df_Liprec_TG_Salar de Uyuni</t>
   </si>
   <si>
-    <t>bf1e73248248423280899044be73fd0e</t>
+    <t>20f396939d894cab9a601b5ce8f60455</t>
   </si>
   <si>
     <t>df_Liprec_TG_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>8aebce218ce4469b83d7a8006c586f9a</t>
+    <t>3a3c4988cd704d6f9d714578157b4a64</t>
   </si>
   <si>
     <t>df_Liprec_TG_Salar del Rincon</t>
   </si>
   <si>
-    <t>26e0f6c0bad345658899045ab7415de4</t>
+    <t>7f7b2e88542f456d834fa0affcedae0c</t>
   </si>
   <si>
     <t>df_Liprec_TG_Silver Peak</t>
   </si>
   <si>
-    <t>8edf042866f64f38bb2961f1ed3ec96e</t>
+    <t>14f045151f5c48e8825b3d96aae8baeb</t>
   </si>
   <si>
     <t>df_centrifuge_general_1_Silver Peak</t>
@@ -1285,7 +1285,7 @@
     <t>df_Liprec_TG_Tres Quebradas</t>
   </si>
   <si>
-    <t>a94cf650ba414a46a661dce6d947fd22</t>
+    <t>55b5d64d735e4c06aef4d9b0bfb0f3ae</t>
   </si>
   <si>
     <t>df_centrifuge_general_1_Tres Quebradas</t>
@@ -1294,7 +1294,7 @@
     <t>df_Liprec_TG_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>2af754195922453f92185f2664be95ea</t>
+    <t>4c6a4fff652b4d0fa0be188e066e8d19</t>
   </si>
   <si>
     <t>df_triple_evaporator_Upper Rhine Graben</t>
@@ -1303,7 +1303,7 @@
     <t>df_Mg_removal_quicklime_East Taijinar</t>
   </si>
   <si>
-    <t>9667158f54ab4de5b4c16daee974ec62</t>
+    <t>557f7f5194404e69861c0b2c7449dd0f</t>
   </si>
   <si>
     <t>df_Mg_removal_quicklime</t>
@@ -1321,7 +1321,7 @@
     <t>df_Mg_removal_quicklime_Maricunga</t>
   </si>
   <si>
-    <t>336458654db341f199dafb2b9e22d97a</t>
+    <t>d5e400e08b984433b7cf281de451d679</t>
   </si>
   <si>
     <t>df_centrifuge_purification_sodaash_Maricunga</t>
@@ -1330,7 +1330,7 @@
     <t>df_Mg_removal_quicklime_Salar de Atacama</t>
   </si>
   <si>
-    <t>72cd8b502d0147d094433ddf5929fbec</t>
+    <t>78e1d35e4c5041e4bc5e3097ee82556e</t>
   </si>
   <si>
     <t>df_centrifuge_purification_sodaash_Salar de Atacama</t>
@@ -1339,7 +1339,7 @@
     <t>df_Mg_removal_quicklime_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>8ec2670d843248ecb6b6065c20c68f55</t>
+    <t>1b48395898a1454f85c9e636a0730dd5</t>
   </si>
   <si>
     <t>df_centrifuge_purification_sodaash_Salar de Cauchari-Olaroz</t>
@@ -1348,19 +1348,19 @@
     <t>df_Mg_removal_quicklime_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>589972f27c1748cb841cb94640d09976</t>
+    <t>a5fd9847b0204a42834dfee77c182e98</t>
   </si>
   <si>
     <t>df_Mg_removal_quicklime_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>1ccf228a985841ecacf8bc33822843e2</t>
+    <t>eea299f576454ca2b38b70f476c5fdd8</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash_Fenix</t>
   </si>
   <si>
-    <t>44250ca020ca4739b7399071716ff3cf</t>
+    <t>cff4820af7d8450895e8c0fc6e98bb8d</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash</t>
@@ -1372,7 +1372,7 @@
     <t>df_Mg_removal_sodaash_Kachi</t>
   </si>
   <si>
-    <t>cd5c9436bb7947a38adea2478b37a5b7</t>
+    <t>022068ce93094cceb75b10498cee8088</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Kachi</t>
@@ -1381,7 +1381,7 @@
     <t>df_Mg_removal_sodaash_Maricunga</t>
   </si>
   <si>
-    <t>e5c52a17daaa450184bd1e0336a236ad</t>
+    <t>73a267cd13c2415e87b19d19e3fa6113</t>
   </si>
   <si>
     <t>df_centrifuge_general_1_Maricunga</t>
@@ -1390,19 +1390,19 @@
     <t>df_Mg_removal_sodaash_Pozuelos</t>
   </si>
   <si>
-    <t>974607ecd9e7493b9c9a4e4e578bec87</t>
+    <t>87ba77ff095a432f91b5ecbc4e3af2c3</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash_Sal de Vida</t>
   </si>
   <si>
-    <t>718accd4d04b40b19bf3453f2958b776</t>
+    <t>56695bbe66f547a2a792d4d8480ef789</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash_Sal de los Angeles</t>
   </si>
   <si>
-    <t>5948dec56b1c48e287689e2efe85d0d0</t>
+    <t>3bd3947936514c039532ea3e91b740ba</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Sal de los Angeles</t>
@@ -1411,13 +1411,13 @@
     <t>df_Mg_removal_sodaash_Salar de Arizaro</t>
   </si>
   <si>
-    <t>f13acd4549ec4af3be187345626680c2</t>
+    <t>d350ceedac654149b9f9bb8a2a651a95</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash_Salar de Atacama</t>
   </si>
   <si>
-    <t>d5351d1efc9e4a26b7bd450274bb65fe</t>
+    <t>02832ea7522648fdba0eaf2c53a7fb7a</t>
   </si>
   <si>
     <t>df_centrifuge_general_1_Salar de Atacama</t>
@@ -1426,13 +1426,13 @@
     <t>df_Mg_removal_sodaash_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>4a011dcc61344441a08d5671a1d25a2a</t>
+    <t>9c1b2744e0094632bd4efb7f8f0158ae</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash_Salar de Centenario</t>
   </si>
   <si>
-    <t>d7eed77ec41a44298e9830e41b928db4</t>
+    <t>0a2ca80efe774c2f993ed233926e8a10</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar de Centenario</t>
@@ -1441,19 +1441,19 @@
     <t>df_Mg_removal_sodaash_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>e288dca113c642d5bb00780d7462bc68</t>
+    <t>89749ffbad9b4e60aa575b24aa5380e3</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash_Salar de Tolillar</t>
   </si>
   <si>
-    <t>b36833b0bf4d4cb4911571e12ad60415</t>
+    <t>2c7834947ff24903bb5cd4e7be4504dd</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash_Salar de Uyuni</t>
   </si>
   <si>
-    <t>f2900df94e67498f87c6e8d87866b31f</t>
+    <t>dd4789b9beb444e29acdbb24207ca33a</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar de Uyuni</t>
@@ -1462,13 +1462,13 @@
     <t>df_Mg_removal_sodaash_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>3f939eeeb7314945a66b87ace79d0633</t>
+    <t>222712ef8ae1468a8cedd5e1de0a3029</t>
   </si>
   <si>
     <t>df_Mg_removal_sodaash_Salar del Rincon</t>
   </si>
   <si>
-    <t>8618b92cfe204b5ea477fdf349dc38f4</t>
+    <t>1be5cce4469740f58fb0f766fff584c1</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar del Rincon</t>
@@ -1477,13 +1477,13 @@
     <t>df_Mg_removal_sodaash_Tres Quebradas</t>
   </si>
   <si>
-    <t>c8b58c8696fa464e9198e7c744371418</t>
+    <t>892f0b3da8de469fbd40bc5d7a555e54</t>
   </si>
   <si>
     <t>df_MnZn_removal_lime_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>6f9bf9a5622c44d19884e8e6afe20c5a</t>
+    <t>919e65c45a4f45908b90ad029e012ebc</t>
   </si>
   <si>
     <t>df_MnZn_removal_lime</t>
@@ -1495,7 +1495,7 @@
     <t>df_SiFe_removal_limestone</t>
   </si>
   <si>
-    <t>d634e3cf90664b6b893546cf62a2a2f7</t>
+    <t>98f0ef52e397427e82474cd53bceafca</t>
   </si>
   <si>
     <t>Lithium</t>
@@ -1507,7 +1507,7 @@
     <t>limestone, crushed, washed</t>
   </si>
   <si>
-    <t>bc2c63b0f0eb4117a5b8a499b11197fa</t>
+    <t>fd1d962ab57b4b8b8ea1c1be4412fce5</t>
   </si>
   <si>
     <t>df_sulfate_removal_calciumchloride_East Taijinar</t>
@@ -1516,49 +1516,49 @@
     <t>df_sulfate_removal_calciumchloride</t>
   </si>
   <si>
-    <t>050fbb000a3e48a78b15b84f51ee445e</t>
-  </si>
-  <si>
-    <t>ec0dc66969724ad78ed19869715757e5</t>
+    <t>71c4469d88a345dcb75a4709f6bd46a6</t>
+  </si>
+  <si>
+    <t>0a9fdda29c4c48b0bc6ede8d5c41ec24</t>
   </si>
   <si>
     <t>df_acidification_Pozuelos</t>
   </si>
   <si>
-    <t>02c743248d1f46dcbfbba9d554c681ab</t>
-  </si>
-  <si>
-    <t>669ac81778ca418ba4f57a74fd427b57</t>
+    <t>7019ffae798a4a6c9730753d49e615de</t>
+  </si>
+  <si>
+    <t>95ced045b3324dc894133411ce463ead</t>
   </si>
   <si>
     <t>df_acidification_Salar de Arizaro</t>
   </si>
   <si>
-    <t>62f532514abf460580aa09ff5c9d905a</t>
-  </si>
-  <si>
-    <t>4684d3bb4ec448c08b726ab20f7202ca</t>
+    <t>6223fbf737f045b8a8aedeb82709066d</t>
+  </si>
+  <si>
+    <t>656042e82b74427abae84963eded8c8c</t>
   </si>
   <si>
     <t>df_acidification_Salar de Tolillar</t>
   </si>
   <si>
-    <t>a1e818f4292746ff97b03c992997710e</t>
-  </si>
-  <si>
-    <t>61738976044e40fa8c28113a3e978bed</t>
-  </si>
-  <si>
-    <t>c9f1059ab3254cd480ad378c40a5e225</t>
-  </si>
-  <si>
-    <t>a65f5a20601f4a82b6515d1767315b4d</t>
+    <t>42e5e81729ef42299e4e4d54097e1948</t>
+  </si>
+  <si>
+    <t>0ad4d34b351648569e34a1d06d753d9c</t>
+  </si>
+  <si>
+    <t>982d288a3dba48b7b358e319e8ed7710</t>
+  </si>
+  <si>
+    <t>2e7cc62e1aa943128c2c8e0c69f7f190</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Chaerhan</t>
   </si>
   <si>
-    <t>0fe80752c9714e9484ec8df7e422d3fe</t>
+    <t>3e171f4d8d354f25a94fe6b1d78713c2</t>
   </si>
   <si>
     <t>df_centrifuge_BG</t>
@@ -1567,7 +1567,7 @@
     <t>df_centrifuge_BG_East Taijinar</t>
   </si>
   <si>
-    <t>454a87e4398141b88432e2cbe93c59a9</t>
+    <t>6cc3678281924b5d8232e016bd39468b</t>
   </si>
   <si>
     <t>waste_liquid_EaTai_East Taijinar</t>
@@ -1579,25 +1579,25 @@
     <t>df_centrifuge_BG_Fenix</t>
   </si>
   <si>
-    <t>0e14df88b191404f8259c8cf0906f2e9</t>
+    <t>34b6ed7ad5a84e4a8b2a15b17c198849</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Kachi</t>
   </si>
   <si>
-    <t>d7c99102ff8c4af7b5523534968e0dd1</t>
+    <t>5870e07d1ec3472694db7730d45b1c55</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Lakkor Tso</t>
   </si>
   <si>
-    <t>55e44fc259084a7fa1070e190fc53a88</t>
+    <t>2a5750bce1d541038e7bb83ce564591e</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Maricunga</t>
   </si>
   <si>
-    <t>c72f8cc355e544918e2e47cc64db4153</t>
+    <t>41adb45dc93d48b9a7fb0cd0a878115a</t>
   </si>
   <si>
     <t>waste_liquid_Mari_Maricunga</t>
@@ -1609,37 +1609,37 @@
     <t>df_centrifuge_BG_Pozuelos</t>
   </si>
   <si>
-    <t>0c8e2adf580f4320bb53f26dda31fab0</t>
+    <t>447f1fe2acec47ce80f08935aeb986f0</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>22b5f545e2c947f28bddea67d8dfcf24</t>
+    <t>02737e2c388d4d3fbd5f51b149b45275</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Sal de Vida</t>
   </si>
   <si>
-    <t>b6fa467d8ca84d45b940e3255404e7cb</t>
+    <t>370c6851973f4140ab55127bd2dc4a75</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Sal de los Angeles</t>
   </si>
   <si>
-    <t>8aacb49b4a2a4d1b95902d63b36bd5a6</t>
+    <t>0f51f18ea555433aac604e354b5c8007</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Salar de Arizaro</t>
   </si>
   <si>
-    <t>4694851fbf054feaa66fe63fc418915f</t>
+    <t>32e8c18bb51f4213845a27653223ae7f</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Salar de Atacama</t>
   </si>
   <si>
-    <t>078245ec612e4aaaaf87cbb4b4b41bd8</t>
+    <t>404b574b5e434ecab4dec8e1d7f3d6f4</t>
   </si>
   <si>
     <t>waste_liquid_Ata_Salar de Atacama</t>
@@ -1651,7 +1651,7 @@
     <t>df_centrifuge_BG_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>8296dc07521b4dd784aac00c68460616</t>
+    <t>84c207cbd2b94a21b84e586641de0cb6</t>
   </si>
   <si>
     <t>waste_liquid_Cau_Salar de Cauchari-Olaroz</t>
@@ -1663,13 +1663,13 @@
     <t>df_centrifuge_BG_Salar de Centenario</t>
   </si>
   <si>
-    <t>bd3e5da9543948b1825df9f2ab727aaa</t>
+    <t>fa90086c282a4784af15bf235ca859e6</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Salar de Olaroz</t>
   </si>
   <si>
-    <t>0392a6b021f64c17a4dafcf610bb9d06</t>
+    <t>4e80dbfe58ca434d9b654c19d3b7c6df</t>
   </si>
   <si>
     <t>waste_liquid_Ola_Salar de Olaroz</t>
@@ -1681,37 +1681,37 @@
     <t>df_centrifuge_BG_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>b40e8bf79d034eb08619b8a74e9968a3</t>
+    <t>6f29bfe2ed3a4129a885372f017d992c</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Salar de Tolillar</t>
   </si>
   <si>
-    <t>53fc8ed8ac2d487ea75d1411581d692b</t>
+    <t>a217c1723c7b45cb899a2c0aa19d82be</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Salar de Uyuni</t>
   </si>
   <si>
-    <t>a41f7cbb2bf24334acabc7ded69b3034</t>
+    <t>ecf2eaf82d6f45b09ee1ccb1cbf181eb</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>c29e8b949acc4b6eadf0cc7d941a15fd</t>
+    <t>cc77bb2169d649c3a83eca5577c50ec4</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Salar del Rincon</t>
   </si>
   <si>
-    <t>d690c60b1ca74c229256d15fcb4af1ae</t>
+    <t>f96bea5a4923403ca6dbd8f68fa29178</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Silver Peak</t>
   </si>
   <si>
-    <t>32fa95049db1418d9d423649fde9a400</t>
+    <t>6c2f2b90abcf493dbabb0d31da9bcf8d</t>
   </si>
   <si>
     <t>waste_liquid_Sil_Silver Peak</t>
@@ -1723,7 +1723,7 @@
     <t>df_centrifuge_BG_Tres Quebradas</t>
   </si>
   <si>
-    <t>252710080f71430cbe24cfa851cd0538</t>
+    <t>1ca2a4d97dcc46afa970f7a7fabb45f4</t>
   </si>
   <si>
     <t>waste_liquid_TresQ_Tres Quebradas</t>
@@ -1735,13 +1735,13 @@
     <t>df_centrifuge_BG_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>289b3e87da034c5a9c64523d20cb9bb8</t>
+    <t>9b5d706972d440f2a1bb0cd7b7f8b958</t>
   </si>
   <si>
     <t>df_centrifuge_BG_Zhabuye</t>
   </si>
   <si>
-    <t>f8513133bdb5410ca156688d018b83bb</t>
+    <t>acf1985a80f5477a81529d6808ad939f</t>
   </si>
   <si>
     <t>waste_liquid_Zha_Zhabuye</t>
@@ -1753,7 +1753,7 @@
     <t>df_centrifuge_TG_Chaerhan</t>
   </si>
   <si>
-    <t>e3ae2a2ce085496690d4308761da5a87</t>
+    <t>1b5c570cfbec43f1bb8608ae0b361ce6</t>
   </si>
   <si>
     <t>df_centrifuge_TG</t>
@@ -1762,85 +1762,85 @@
     <t>df_centrifuge_TG_East Taijinar</t>
   </si>
   <si>
-    <t>468852c6fa8146a1be76409fad4b0e5d</t>
+    <t>7cacc417674049ff9bd3ab78506f11eb</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Fenix</t>
   </si>
   <si>
-    <t>e16f3df41a364ef39c3fa74d4d0641dd</t>
+    <t>dd871438765d4bb9bb602932efa1cc23</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Kachi</t>
   </si>
   <si>
-    <t>a004e9f7010d46c883fbba45b95a4375</t>
+    <t>8d3a41b022a04fa4b7b59fd3128802ee</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Lakkor Tso</t>
   </si>
   <si>
-    <t>d8d9b698561647bbac2dfb9bf017fdcd</t>
+    <t>22160dff2d2140309cd5600e56fe5926</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Maricunga</t>
   </si>
   <si>
-    <t>77dafba34374440aa713aa23046937d9</t>
+    <t>9ac5fff1504f444aab0e83f7c0e2ebd2</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Pozuelos</t>
   </si>
   <si>
-    <t>6b46c2902ae84e8f8a01e1d7a1ad617d</t>
+    <t>817983897daa4b9eafdf198a32ded18b</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>04180f1f3f6142bc9957f83ad8f2564a</t>
+    <t>6806be4ac7254e49afbaf750af2b1d7e</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Sal de Vida</t>
   </si>
   <si>
-    <t>4b1bedd4db424c95a56455d401a8138a</t>
+    <t>b263a9d54998459994ad6841b6d3fb3e</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Sal de los Angeles</t>
   </si>
   <si>
-    <t>7e62f7036d1f421aab8d40d0e3d70210</t>
+    <t>5bb97c71e4614e76aacfcd9edb2f8d0e</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar de Arizaro</t>
   </si>
   <si>
-    <t>67d2961ebb684cbcb2dd9ab1c48ec95d</t>
+    <t>d0f417d9ead14d859d7457c6112ce62f</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar de Atacama</t>
   </si>
   <si>
-    <t>643a833d320f4c4ca731033b4bdd1768</t>
+    <t>be27bd4ad4fe49f79fd80420ccb394fd</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>e1789314af73462dbefac712381bb364</t>
+    <t>721a982cadfc4266bdcac6f76b78c747</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar de Centenario</t>
   </si>
   <si>
-    <t>58b31c9c2d40407e81614f26ead5b8fc</t>
+    <t>87100ae6ac0e4b409c3873fd9d42a66c</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar de Olaroz</t>
   </si>
   <si>
-    <t>b9a2d8814eb0425299a01a701b87a050</t>
+    <t>a792419614d74893804c5840c82b75cd</t>
   </si>
   <si>
     <t>df_washing_TG_Salar de Olaroz</t>
@@ -1852,37 +1852,37 @@
     <t>df_centrifuge_TG_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>7e2b0b9b6d6241b1b63f1cd9358c1653</t>
+    <t>52126f1d172d43648f17a99c98bd304a</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar de Tolillar</t>
   </si>
   <si>
-    <t>d8347f2f04cf4150b051d726589c229f</t>
+    <t>71b958e9ae8245d2a61372db77750d0b</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar de Uyuni</t>
   </si>
   <si>
-    <t>6d872c4a35d44a11a14e7b673648d5a3</t>
+    <t>4fa2922579844ed3a392f564929fd80e</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>7a56a19b0eb148a2ac250d09109c1496</t>
+    <t>07982da14766460f894f9b3035106c71</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Salar del Rincon</t>
   </si>
   <si>
-    <t>de44b08b980f4fafbced69b75f61a650</t>
+    <t>86806a82ec4b4405b79d3fcd13990df3</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Silver Peak</t>
   </si>
   <si>
-    <t>e009fad5948a4cfd835a04ecf45a8143</t>
+    <t>256ff1944d624336babc35a4e6c3659d</t>
   </si>
   <si>
     <t>df_washing_TG_Silver Peak</t>
@@ -1891,22 +1891,22 @@
     <t>df_centrifuge_TG_Tres Quebradas</t>
   </si>
   <si>
-    <t>327c2b5677e5415b8d79334740236251</t>
+    <t>55dd5c456b9d4723af6a584e3e7a30b5</t>
   </si>
   <si>
     <t>df_centrifuge_TG_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>5651926d617740d0b2007e73dd325c4f</t>
-  </si>
-  <si>
-    <t>34be18bc8e494c1d9ad6840cf60bb85a</t>
-  </si>
-  <si>
-    <t>1a479dafc3ba4f34b3fadd86e37b51db</t>
-  </si>
-  <si>
-    <t>2900c464f0d1427894d6f0e06ea79683</t>
+    <t>0f741d33f8ef4a4f99299754e6f3f8da</t>
+  </si>
+  <si>
+    <t>4a875487a2ca4eb099ded5da073947df</t>
+  </si>
+  <si>
+    <t>27efafb376b3475eb88ab0cd4af6ec71</t>
+  </si>
+  <si>
+    <t>fab974d5430943129fe01228d85de07d</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar de Olaroz</t>
@@ -1915,28 +1915,28 @@
     <t>df_centrifuge_general_1_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>282f18be835c4120990d14bcc3bff4b5</t>
+    <t>f265c567db264ec7891e85bc435bf4ba</t>
   </si>
   <si>
     <t>df_centrifuge_general_1_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>609e08c394204034a37885ba19f8914c</t>
-  </si>
-  <si>
-    <t>33e98086ca8d41cd8fb4e5d11904915b</t>
+    <t>43c785be2c004d3f82e355d0d974b5ab</t>
+  </si>
+  <si>
+    <t>5fd0d28d9fbb49389f287ef5c12e5956</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Silver Peak</t>
   </si>
   <si>
-    <t>3db1450893704b87845c4e91be2444ad</t>
+    <t>39498357a64b4df5b4f9bc1a7fa44335</t>
   </si>
   <si>
     <t>df_centrifuge_general_1_Zhabuye</t>
   </si>
   <si>
-    <t>44a79a4e66bb4db2913762e19776a9a2</t>
+    <t>ca361deddb8b40b8a0dc8985284021ed</t>
   </si>
   <si>
     <t>df_washing_general_Zhabuye</t>
@@ -1948,7 +1948,7 @@
     <t>df_centrifuge_general_2_Salar de Olaroz</t>
   </si>
   <si>
-    <t>68eed73b87d84409ac587d3c64a1cd09</t>
+    <t>3231c26072c04fddb2b5c135b6cca93f</t>
   </si>
   <si>
     <t>df_centrifuge_general_2</t>
@@ -1960,7 +1960,7 @@
     <t>df_centrifuge_general_2_Silver Peak</t>
   </si>
   <si>
-    <t>76e09655177040eb8b631d1c0778a00c</t>
+    <t>d53fe51a79684a868618dd54e4db2c45</t>
   </si>
   <si>
     <t>df_dissolution_Silver Peak</t>
@@ -1969,7 +1969,7 @@
     <t>df_centrifuge_general_2_Zhabuye</t>
   </si>
   <si>
-    <t>e75c5d3aa7ce442c9302413391ed0db9</t>
+    <t>2caa11814cd749639bcb87bd292c96c2</t>
   </si>
   <si>
     <t>df_dissolution_Zhabuye</t>
@@ -1978,70 +1978,70 @@
     <t>df_centrifuge_purification_quicklime_East Taijinar</t>
   </si>
   <si>
-    <t>038a29d6655b4cf28532769d51e75a50</t>
+    <t>ee31540a752146aebc60cac3305ede12</t>
   </si>
   <si>
     <t>df_centrifuge_purification_quicklime_Maricunga</t>
   </si>
   <si>
-    <t>128ee4302c4446f2830a2cad308f27f8</t>
-  </si>
-  <si>
-    <t>c6405fd5d2a941e893c6ffd216ba9c18</t>
+    <t>68385e55db9347ceabfc06c1fce7c917</t>
+  </si>
+  <si>
+    <t>859a74ecd64540869066f6f6f3202770</t>
   </si>
   <si>
     <t>df_centrifuge_purification_quicklime_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>eeb377288d7643679b873ad18c7163d6</t>
+    <t>27febddf6c5f412da492420eae346da2</t>
   </si>
   <si>
     <t>df_centrifuge_purification_quicklime_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>4ab73b303ad14670bc41ff62578a9a1f</t>
+    <t>a33d44cf438449fbbc2ed648cc7041f3</t>
   </si>
   <si>
     <t>df_centrifuge_purification_quicklime_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>dfd8159297fc4ea186d555be59e269fc</t>
-  </si>
-  <si>
-    <t>2d4911b18979432cabf2eab9fedffd05</t>
+    <t>bce625e0310c481397e946fa25e889eb</t>
+  </si>
+  <si>
+    <t>d5c53c4dc0294bbc8a1ff6ded396fab1</t>
   </si>
   <si>
     <t>df_centrifuge_purification_sodaash_Sal de Vida</t>
   </si>
   <si>
-    <t>7ccff6e8d8bf42efa6951996674c6b81</t>
-  </si>
-  <si>
-    <t>87b2593c1d7243738767d92b0b6351d7</t>
-  </si>
-  <si>
-    <t>f434c71076694c22ad263c872046f0d1</t>
+    <t>c4a72b0dff2b42bcb781d7cf1ad08a98</t>
+  </si>
+  <si>
+    <t>42056c773509449bb7474fd3d95d557e</t>
+  </si>
+  <si>
+    <t>7dabda6973c6406b965a7745fc5d5013</t>
   </si>
   <si>
     <t>df_centrifuge_purification_sodaash_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>5da9913294d940f4b9c759c416b6dae5</t>
+    <t>11eccf2c5aa14dbc84fee0a5f6d50d3c</t>
   </si>
   <si>
     <t>df_centrifuge_purification_sodaash_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>b3081c9dfe644970897ad0320ccd4431</t>
-  </si>
-  <si>
-    <t>fddc5eb4fabb41afb0fd3b1287811ea7</t>
+    <t>933615f89f4d494ab2a610153659603f</t>
+  </si>
+  <si>
+    <t>bdde59a32cfe4b2fa04e192aa91dc0b1</t>
   </si>
   <si>
     <t>df_centrifuge_wash_Chaerhan</t>
   </si>
   <si>
-    <t>2fbaead3c0654dcba9824307f76899e2</t>
+    <t>56a56accca6b43b0b6f84a76031e30f9</t>
   </si>
   <si>
     <t>df_centrifuge_wash</t>
@@ -2056,7 +2056,7 @@
     <t>df_centrifuge_wash_East Taijinar</t>
   </si>
   <si>
-    <t>840bbe80fc5848c89c2324853f421787</t>
+    <t>bbc7d8b6b493440e9ec0119c381fe3ce</t>
   </si>
   <si>
     <t>df_washing_BG_East Taijinar</t>
@@ -2065,7 +2065,7 @@
     <t>df_centrifuge_wash_Fenix</t>
   </si>
   <si>
-    <t>acd9bd123def4280a3150e1d9a3268d3</t>
+    <t>99b38dc518404e97b288d891798d4313</t>
   </si>
   <si>
     <t>df_washing_BG_Fenix</t>
@@ -2074,7 +2074,7 @@
     <t>df_centrifuge_wash_Kachi</t>
   </si>
   <si>
-    <t>a8c1bd30f6034b3a92ea13885f643d66</t>
+    <t>d20805cd28e1437c89f6246c140306de</t>
   </si>
   <si>
     <t>df_washing_BG_Kachi</t>
@@ -2083,7 +2083,7 @@
     <t>df_centrifuge_wash_Lakkor Tso</t>
   </si>
   <si>
-    <t>25d60c58a23a4095a6f7c8a329083cf4</t>
+    <t>cf6defc80e9e4d6d96e973835a12af1a</t>
   </si>
   <si>
     <t>df_washing_BG_Lakkor Tso</t>
@@ -2092,7 +2092,7 @@
     <t>df_centrifuge_wash_Maricunga</t>
   </si>
   <si>
-    <t>f047d640b8d4456c8a2e628d883759b7</t>
+    <t>baebce124cf344aab88189ab62444c59</t>
   </si>
   <si>
     <t>df_washing_BG_Maricunga</t>
@@ -2101,13 +2101,13 @@
     <t>df_centrifuge_wash_Pozuelos</t>
   </si>
   <si>
-    <t>827d45396f4646d7ad76de8a8c9f4150</t>
+    <t>5b7dde33319d471eb803e583ae067198</t>
   </si>
   <si>
     <t>df_centrifuge_wash_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>27fa29425dfb4809a708b64a93adfe07</t>
+    <t>274b634662794346b2841f5362f425ea</t>
   </si>
   <si>
     <t>df_washing_BG_Qinghai Yiliping</t>
@@ -2116,13 +2116,13 @@
     <t>df_centrifuge_wash_Sal de Vida</t>
   </si>
   <si>
-    <t>9759333c7cfd40c7b07745eaab1b8e47</t>
+    <t>79def241b1dd4a8abeb475663c4089c5</t>
   </si>
   <si>
     <t>df_centrifuge_wash_Sal de los Angeles</t>
   </si>
   <si>
-    <t>81513a987e634a19bcb07bad1250617f</t>
+    <t>5424bd0917cc44f88ebb9951dd182c9e</t>
   </si>
   <si>
     <t>df_washing_BG_Sal de los Angeles</t>
@@ -2131,13 +2131,13 @@
     <t>df_centrifuge_wash_Salar de Arizaro</t>
   </si>
   <si>
-    <t>6597bf036fd24b92a0a1668967812433</t>
+    <t>a3a70d4d4c8d4178a71f9824cc277289</t>
   </si>
   <si>
     <t>df_centrifuge_wash_Salar de Atacama</t>
   </si>
   <si>
-    <t>1e15d9807db643b98a0270927faefe3a</t>
+    <t>34aa3b3a5db64306a65e8191c2f0181e</t>
   </si>
   <si>
     <t>df_washing_BG_Salar de Atacama</t>
@@ -2146,7 +2146,7 @@
     <t>df_centrifuge_wash_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>76f5718d034b4671b8b684c81acec265</t>
+    <t>27dffec9886846f1806c1e22be740872</t>
   </si>
   <si>
     <t>df_washing_BG_Salar de Cauchari-Olaroz</t>
@@ -2155,7 +2155,7 @@
     <t>df_centrifuge_wash_Salar de Centenario</t>
   </si>
   <si>
-    <t>bffed1f94bad452cb5fc0ad822bdcd11</t>
+    <t>8d40a767324948b3be8805a9c5b6d955</t>
   </si>
   <si>
     <t>df_washing_BG_Salar de Centenario</t>
@@ -2164,7 +2164,7 @@
     <t>df_centrifuge_wash_Salar de Olaroz</t>
   </si>
   <si>
-    <t>46dc064abcbc4fa29d8549a098bd21ed</t>
+    <t>d16576eba7aa4050be9dda0aa02c2436</t>
   </si>
   <si>
     <t>df_washing_BG_Salar de Olaroz</t>
@@ -2173,19 +2173,19 @@
     <t>df_centrifuge_wash_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>9aa29a45125b4c70a3aa40b0b2e07c5e</t>
+    <t>81eeb856ad5a43f9879ed4fee74596f5</t>
   </si>
   <si>
     <t>df_centrifuge_wash_Salar de Tolillar</t>
   </si>
   <si>
-    <t>0641a2ee962d4c66a2a8063e59a39981</t>
+    <t>9457d108ecba46da81db899ed797677d</t>
   </si>
   <si>
     <t>df_centrifuge_wash_Salar de Uyuni</t>
   </si>
   <si>
-    <t>cafb54b3ce2046c09b882e9e1e622562</t>
+    <t>7691d3d26263488fb94d0efcd304cff2</t>
   </si>
   <si>
     <t>df_washing_BG_Salar de Uyuni</t>
@@ -2194,13 +2194,13 @@
     <t>df_centrifuge_wash_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>e538f660dcec4a50ba94de88d62720b2</t>
+    <t>d8b6ba9f10d6437c81b7ebfa713c320b</t>
   </si>
   <si>
     <t>df_centrifuge_wash_Salar del Rincon</t>
   </si>
   <si>
-    <t>f3ca4744b2a049ac870b9916c2147268</t>
+    <t>083856a5edc2436789c14b9a5ea32081</t>
   </si>
   <si>
     <t>df_washing_BG_Salar del Rincon</t>
@@ -2209,7 +2209,7 @@
     <t>df_centrifuge_wash_Silver Peak</t>
   </si>
   <si>
-    <t>b87b3c8f0cd44411a8dabe014c2bdb8b</t>
+    <t>0ca8e93fbd2849fe91f09006750b87fd</t>
   </si>
   <si>
     <t>df_washing_BG_Silver Peak</t>
@@ -2218,7 +2218,7 @@
     <t>df_centrifuge_wash_Tres Quebradas</t>
   </si>
   <si>
-    <t>893aa05a7ac044698de44ebaf4c0eab1</t>
+    <t>0f024b186b8e4cb2a9072568b437b851</t>
   </si>
   <si>
     <t>df_washing_BG_Tres Quebradas</t>
@@ -2227,7 +2227,7 @@
     <t>df_centrifuge_wash_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>0c8b975d1f3b436b8c02b147d6ed289e</t>
+    <t>ed4b4ce261054797b722bbef44df5548</t>
   </si>
   <si>
     <t>df_washing_BG_Upper Rhine Graben</t>
@@ -2236,43 +2236,43 @@
     <t>df_centrifuge_wash_Zhabuye</t>
   </si>
   <si>
-    <t>24620200e5584154abc2bf2f046d5c49</t>
+    <t>f8a9adb127b84002a2270ae6e434bd3b</t>
   </si>
   <si>
     <t>df_washing_BG_Zhabuye</t>
   </si>
   <si>
-    <t>83af4dfad24449dd8df11ec01783d56c</t>
+    <t>dcd076750739465dbc2518ac8a981250</t>
   </si>
   <si>
     <t>df_washing_TG_Chaerhan</t>
   </si>
   <si>
-    <t>da1ea2420fc44718b3a1d326389011bd</t>
+    <t>c185a94810e9419eb19fbb36fe967aa0</t>
   </si>
   <si>
     <t>df_washing_TG_East Taijinar</t>
   </si>
   <si>
-    <t>be00646873e046a2887b187b9c44ab5b</t>
+    <t>651e5e4444124a05ba7fe339394e1628</t>
   </si>
   <si>
     <t>df_washing_TG_Fenix</t>
   </si>
   <si>
-    <t>7b7cdd5dadc44d0789a82c15b1d35345</t>
+    <t>8fdbe434736f4f02895cd17dc3a09e2c</t>
   </si>
   <si>
     <t>df_washing_TG_Kachi</t>
   </si>
   <si>
-    <t>94287672c4a042ef8ee1f2b28b2e04ed</t>
+    <t>9ef6754b54a844308b3b6153685d5078</t>
   </si>
   <si>
     <t>df_washing_TG_Lakkor Tso</t>
   </si>
   <si>
-    <t>6863f82973094b56a2b9c18d10729497</t>
+    <t>be29c6a76a2747af880a835c670bb99a</t>
   </si>
   <si>
     <t>df_washing_TG_Maricunga</t>
@@ -2281,10 +2281,10 @@
     <t>df_dissolution_Pozuelos</t>
   </si>
   <si>
-    <t>7b38d9c939d54861ba75978f97c67d4f</t>
-  </si>
-  <si>
-    <t>af3d2c46c93b46dea1edcfb3d61b1182</t>
+    <t>c183dcc2cb8b4b1faebcf1a0b0794ae1</t>
+  </si>
+  <si>
+    <t>bd5b43147b944a07bf985b214a75cb6c</t>
   </si>
   <si>
     <t>df_washing_TG_Qinghai Yiliping</t>
@@ -2293,10 +2293,10 @@
     <t>df_dissolution_Sal de Vida</t>
   </si>
   <si>
-    <t>2db9deb0da57460e891478cf048b6608</t>
-  </si>
-  <si>
-    <t>3579ab1c07e8417e8229c88476b3804e</t>
+    <t>7e7a4cd1143e4a9c9e2a837565191454</t>
+  </si>
+  <si>
+    <t>63e49b2ae49f494981700cd972246c13</t>
   </si>
   <si>
     <t>df_washing_TG_Sal de los Angeles</t>
@@ -2305,43 +2305,43 @@
     <t>df_dissolution_Salar de Arizaro</t>
   </si>
   <si>
-    <t>e1375f0dce724431800f85f9de571fb9</t>
-  </si>
-  <si>
-    <t>688305b8dadf40d080922bc94aec1e93</t>
+    <t>94ba035fac6b424abeb018506c518a22</t>
+  </si>
+  <si>
+    <t>096aef30928f4c96bfc4b10b87274c6d</t>
   </si>
   <si>
     <t>df_washing_TG_Salar de Atacama</t>
   </si>
   <si>
-    <t>7b3b1fa05af5487e885b6c2999e99bb3</t>
+    <t>60a91c18dc994b7d8043ed02e494ef2e</t>
   </si>
   <si>
     <t>df_washing_TG_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>ba2068d9cce5412ba9dece204563bf76</t>
+    <t>3b703f6471e84a748f40d4a738278d83</t>
   </si>
   <si>
     <t>df_washing_TG_Salar de Centenario</t>
   </si>
   <si>
-    <t>b56bd5b32736472e8a5e61575f6d2e80</t>
+    <t>541714a3bd064b4994b3ba0493205ee4</t>
   </si>
   <si>
     <t>df_dissolution_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>9755f7d62cfa4757b7670f474160c586</t>
+    <t>9bf7f4c2aa684b8093b0938ee5e96c12</t>
   </si>
   <si>
     <t>df_dissolution_Salar de Tolillar</t>
   </si>
   <si>
-    <t>b726db2738f1448db68194951093a666</t>
-  </si>
-  <si>
-    <t>e336cfba412d4b9b8015fd65e17f6857</t>
+    <t>05bd50a1557a42c3bf32c9c5878fc1cf</t>
+  </si>
+  <si>
+    <t>68fe54ad3b79403fa56a9a9bf0fd3dd9</t>
   </si>
   <si>
     <t>df_washing_TG_Salar de Uyuni</t>
@@ -2350,37 +2350,37 @@
     <t>df_dissolution_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>fc4458f9d9904e2f94757194b5d1c947</t>
-  </si>
-  <si>
-    <t>81fcc746c58e4be19b55430db6305c0a</t>
+    <t>5d1a0548697540d68c145e15711f9f51</t>
+  </si>
+  <si>
+    <t>0002b53e1ab54084b74df503e0351ef4</t>
   </si>
   <si>
     <t>df_washing_TG_Salar del Rincon</t>
   </si>
   <si>
-    <t>8a18572128894e1fbdeea732eb3ec95c</t>
-  </si>
-  <si>
-    <t>853ad46e1e094b298c6f904b16ca60a1</t>
+    <t>e2aa2bd4792b498ba63410b4914846e8</t>
+  </si>
+  <si>
+    <t>cb7a66dab8da4de8864db4792a96302d</t>
   </si>
   <si>
     <t>df_washing_TG_Tres Quebradas</t>
   </si>
   <si>
-    <t>420269bf7c454eda97f60ea179504366</t>
+    <t>831559d10b93492da598c5ab7bae208f</t>
   </si>
   <si>
     <t>df_washing_TG_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>aabe1496fe5849249051feb4191a1c11</t>
+    <t>54826b4f75fb47f09e49534f7cc43c5b</t>
   </si>
   <si>
     <t>df_electrodialysis_East Taijinar</t>
   </si>
   <si>
-    <t>e1e99efe4f6847a985468b623ea32fe1</t>
+    <t>332a4e176fb743e8bd64995d61a6483d</t>
   </si>
   <si>
     <t>df_electrodialysis</t>
@@ -2389,7 +2389,7 @@
     <t>df_ion_exchange_L_East Taijinar</t>
   </si>
   <si>
-    <t>e54546077a044823bb342ea08e3211d4</t>
+    <t>7aa9b0d0098b4292b1f78a80373821bf</t>
   </si>
   <si>
     <t>machine operation, diesel, &gt;= 74.57 kW, high load factor</t>
@@ -2410,103 +2410,103 @@
     <t>salt tailing from potash mine</t>
   </si>
   <si>
-    <t>c10d7019629b444489be959ebfb72440</t>
-  </si>
-  <si>
-    <t>75bca6edbcca4f0d9859c220a4fe9f82</t>
-  </si>
-  <si>
-    <t>b8dcdd5b5d5f4293aefea4842874ac9b</t>
-  </si>
-  <si>
-    <t>1430c07e40bc47b18fa4d28aeac1feb8</t>
-  </si>
-  <si>
-    <t>0394359e98d84fecbc192916d2e2fec2</t>
+    <t>b28c26b281ee4c7dbc206433864fafa2</t>
+  </si>
+  <si>
+    <t>81d13aa8f87846d297695d210849ae26</t>
+  </si>
+  <si>
+    <t>3e76c161da5b4d99a6fb232b6245f1b6</t>
+  </si>
+  <si>
+    <t>9f70842cbeb24bd2aa60a33a28c16009</t>
+  </si>
+  <si>
+    <t>c845d3516fd647b0a903f54bc50af9ff</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Pozuelos</t>
   </si>
   <si>
-    <t>3e032297d8ba4707959af7ccdb225887</t>
-  </si>
-  <si>
-    <t>f049375eec3d4a66b0dc5af8d998028f</t>
+    <t>858e0caab13f42f5bb9dc13ec7f4667a</t>
+  </si>
+  <si>
+    <t>e8ec8974e952456ba16ed62dd15d01e1</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Sal de Vida</t>
   </si>
   <si>
-    <t>de828d0de034445cb25a585556d3eb91</t>
-  </si>
-  <si>
-    <t>84bb73c7562942d68a08f551e2d11358</t>
+    <t>2c0297da2fc84a758fd522f4f6c1757a</t>
+  </si>
+  <si>
+    <t>13e1e8285a09440a8f19196d7e1c0b85</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar de Arizaro</t>
   </si>
   <si>
-    <t>aaf0854865694bd1b28c7e61565bded0</t>
+    <t>9abb1df55d5b48aa81a3702956b76e2b</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar de Atacama</t>
   </si>
   <si>
-    <t>472d4a8107f24781b379cec637366990</t>
-  </si>
-  <si>
-    <t>e205a503adec4dd0a726ca0465d8a151</t>
-  </si>
-  <si>
-    <t>fff589113d2d4b0c88ea8e3b8b15f5fb</t>
-  </si>
-  <si>
-    <t>c6f69235c874406a994d9c21f482262a</t>
+    <t>e43932fe5a0d4ee6a8d5d22ea9e3547e</t>
+  </si>
+  <si>
+    <t>900ce602f1f44cd59e567f3f85cf3028</t>
+  </si>
+  <si>
+    <t>e755d02be3a74617819aa653baaad475</t>
+  </si>
+  <si>
+    <t>5798d41f5a664d22a1d73349add3bbc6</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>7ea0787bc8b44162905bb3a49f9b2f97</t>
+    <t>8b8ce09db6a04b47a346e0381d75e49e</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar de Tolillar</t>
   </si>
   <si>
-    <t>091b36f734ab4ed4a947b388e160a288</t>
-  </si>
-  <si>
-    <t>d57e086fab564e1c9c5de2ccdb0c3053</t>
+    <t>c84f7ded23ce437fa03986814ddc7336</t>
+  </si>
+  <si>
+    <t>09bf2cdb92cf41579f7bd565497a77ee</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>97b5fc3b7f7e4c3897e910aaa1188fce</t>
-  </si>
-  <si>
-    <t>f1ac49130ed741d78545eef4f9e26668</t>
-  </si>
-  <si>
-    <t>6c85f50b295a49c0b38961cda122afa9</t>
+    <t>0d872112ca2f4edfba316eb24bff52f3</t>
+  </si>
+  <si>
+    <t>155e4b8701ee4ef48955a5039a3296a1</t>
+  </si>
+  <si>
+    <t>81ccab62f82b436bbc75a5f1c5a0e8b1</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Tres Quebradas</t>
   </si>
   <si>
-    <t>1d533e00fcab4493b95cb2e2fc513a84</t>
+    <t>f7160130ebed4525b628487196c80871</t>
   </si>
   <si>
     <t>df_evaporation_ponds_Zhabuye</t>
   </si>
   <si>
-    <t>3a1f1e8745a64be79e2f80d385c4ebd7</t>
+    <t>8d8fa84f70c643b0b1c673a55fbcfe0c</t>
   </si>
   <si>
     <t>df_grinding_Zhabuye</t>
   </si>
   <si>
-    <t>f02db66e26734362a0aa548ec0f099d8</t>
+    <t>ae8c2675abfc422b85ec1faa812c4799</t>
   </si>
   <si>
     <t>df_grinding</t>
@@ -2518,7 +2518,7 @@
     <t>df_ion_exchange_H_2_Salar de Olaroz</t>
   </si>
   <si>
-    <t>3bdf20d2335b4ede85bff81c1f6488a5</t>
+    <t>18972dc2689b4be8a2f88b97d118b999</t>
   </si>
   <si>
     <t>df_ion_exchange_H_2</t>
@@ -2539,7 +2539,7 @@
     <t>df_ion_exchange_H_2_Silver Peak</t>
   </si>
   <si>
-    <t>cfd16c1ff59443f1964ebb0f37342c31</t>
+    <t>d930387513a140fe86a2045b8f47cbd2</t>
   </si>
   <si>
     <t>df_ion_exchange_H_Silver Peak</t>
@@ -2548,61 +2548,61 @@
     <t>df_ion_exchange_H_2_Zhabuye</t>
   </si>
   <si>
-    <t>8cda3a00e6e14b03babf53b7b01e7c9d</t>
+    <t>71026d94ab094530a196a98f4ac3ad3d</t>
   </si>
   <si>
     <t>df_ion_exchange_H_Zhabuye</t>
   </si>
   <si>
-    <t>ee800e36be994a5099580a7ad622e2a5</t>
+    <t>f09a4df0808d40698eb59bea73e0d272</t>
   </si>
   <si>
     <t>df_ion_exchange_H_Sal de Vida</t>
   </si>
   <si>
-    <t>3da249b9dd504eb1a1f916669c0fd0eb</t>
+    <t>5cdeba6687b047bf86d2613c8004ccc3</t>
   </si>
   <si>
     <t>df_ion_exchange_H_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>c8ec07ec16b5462d9c51273c8c610bcb</t>
+    <t>0cf9b84599f6415e83903c6d6c985bec</t>
   </si>
   <si>
     <t>df_sulfate_removal_calciumchloride_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>3e70dd3f4ac4460ea2466ec227a4236c</t>
+    <t>aa6a32a198494e6bab4fb9422629e1f2</t>
   </si>
   <si>
     <t>df_ion_exchange_H_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>37d3f1ddadbf491f840548a1a3fe09e5</t>
-  </si>
-  <si>
-    <t>540128553e11470d95c6eb0c00befd2d</t>
-  </si>
-  <si>
-    <t>1c4319c5f2c241c19823683b6064700b</t>
+    <t>b1747c8011104307a5f07619471df424</t>
+  </si>
+  <si>
+    <t>7b49d5cc66fb4d11b119e2023a5f49ff</t>
+  </si>
+  <si>
+    <t>44b0407268f94175bb0dd014c11e4f50</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Chaerhan</t>
   </si>
   <si>
-    <t>4de24e0d9ed043a589dcef4159cea333</t>
-  </si>
-  <si>
-    <t>3a284158e75d460ea91d4ca2b38c1a20</t>
-  </si>
-  <si>
-    <t>f1de54f810ab4bdd838fe32734380311</t>
+    <t>66b7043c1dac4541951aa8ef90076e45</t>
+  </si>
+  <si>
+    <t>68cfafcff6f149e8aad942bf46727b7c</t>
+  </si>
+  <si>
+    <t>5cf985aca63e43f2931480f840a30666</t>
   </si>
   <si>
     <t>df_triple_evaporator_Fenix</t>
   </si>
   <si>
-    <t>1be4c1a8677b403da9f9a38a8c1ea4d4</t>
+    <t>b7e61b7ec099479ca91d47a7a00925b7</t>
   </si>
   <si>
     <t>df_triple_evaporator_Kachi</t>
@@ -2611,22 +2611,22 @@
     <t>df_ion_exchange_L_Lakkor Tso</t>
   </si>
   <si>
-    <t>6c7545b0c9be426bba5c0592ed3c329c</t>
+    <t>9c9042027f7c4f759e0d137d49732d6b</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Pozuelos</t>
   </si>
   <si>
-    <t>ea8520762a924709b83a475f9314d437</t>
+    <t>39607aa012384e34b916d8ead8d5f881</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>4610e0e4e1c742e39407b87651bdf11f</t>
-  </si>
-  <si>
-    <t>0c05ff5cf6b043f587970df153a148fc</t>
+    <t>3c7a77177f0549069ebdb0b5abc5d86f</t>
+  </si>
+  <si>
+    <t>031d70a1d4a24416b400fc1a1be9b316</t>
   </si>
   <si>
     <t>df_triple_evaporator_Sal de los Angeles</t>
@@ -2635,52 +2635,52 @@
     <t>df_ion_exchange_L_Salar de Arizaro</t>
   </si>
   <si>
-    <t>d8ec3fea15224ff99043e8951af16617</t>
-  </si>
-  <si>
-    <t>8f7ba0749b97445eabe36b2c4afb2f69</t>
+    <t>eac6db114b9a47b495a1dfa7ec5b0180</t>
+  </si>
+  <si>
+    <t>91ec010748e84da59866aeae417a48af</t>
   </si>
   <si>
     <t>df_triple_evaporator_Salar de Centenario</t>
   </si>
   <si>
-    <t>db19f3cb49b045a38c7772398560b9ac</t>
+    <t>169918b63869407198473a3ea7ddef4d</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Salar de Tolillar</t>
   </si>
   <si>
-    <t>bca5a51b32534ec78b10f52a30c1e3ed</t>
-  </si>
-  <si>
-    <t>1121a1063d534742be1c5f679bbc44b2</t>
+    <t>1f088936e7ab4c1e9e830dd6be7bee5d</t>
+  </si>
+  <si>
+    <t>83a7054f40d44acdb33d1f399129ab26</t>
   </si>
   <si>
     <t>df_triple_evaporator_Salar de Uyuni</t>
   </si>
   <si>
-    <t>0c7df904102e4c75add262681561cbc4</t>
+    <t>cf81d56fff5d42f0908e8cf1ccd53b44</t>
   </si>
   <si>
     <t>df_triple_evaporator_Salar del Rincon</t>
   </si>
   <si>
-    <t>82c344d683414bbb9c53b1c536aa05c8</t>
+    <t>015d59df0b91430386b451bbbe37c8f6</t>
   </si>
   <si>
     <t>df_ion_exchange_L_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>42ad5666772a4c51aa1670cd6b981404</t>
-  </si>
-  <si>
-    <t>def9b8538c56499da9154be62bd0b656</t>
+    <t>c8cb917ab2f241bbaa9ee1f3c40aacef</t>
+  </si>
+  <si>
+    <t>7c7aa8870a6843fd9fa9837239f41d54</t>
   </si>
   <si>
     <t>df_nanofiltration_Chaerhan</t>
   </si>
   <si>
-    <t>b97d63b425dc444894f62d41e6e3deb7</t>
+    <t>e189e46020644c498da2d5e32630c6d8</t>
   </si>
   <si>
     <t>df_nanofiltration</t>
@@ -2689,175 +2689,175 @@
     <t>df_nanofiltration_Lakkor Tso</t>
   </si>
   <si>
-    <t>49d26d684ad442bba7c5dad741913803</t>
+    <t>fe4fa087ada74739967d947eb15fb177</t>
   </si>
   <si>
     <t>df_nanofiltration_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>2ed789e650ec49fab27bd1d7c148ad02</t>
-  </si>
-  <si>
-    <t>eb3a35d40e9a4f80a9326fced125f2b6</t>
-  </si>
-  <si>
-    <t>0762323ae91f4f1280e89abaaae0e660</t>
-  </si>
-  <si>
-    <t>a2f92ff387ff4f1083360fdc59488f14</t>
-  </si>
-  <si>
-    <t>27451f8fc03048f9a2e5a7e9607c3482</t>
+    <t>de7262685ed04b86bad595aeba26642d</t>
+  </si>
+  <si>
+    <t>eb9c9f04fd5043038fa4c485fb58280f</t>
+  </si>
+  <si>
+    <t>294757a0b7ad4c7a98b580a61cac4b90</t>
+  </si>
+  <si>
+    <t>5d3cf3e4373d43c4828d8296195a0fd0</t>
+  </si>
+  <si>
+    <t>3819801700924fc6b86f02dfd8956456</t>
   </si>
   <si>
     <t>df_reverse_osmosis_Upper Rhine Graben</t>
   </si>
   <si>
-    <t>491240a56b3d4a82b88a6e330a251cdc</t>
+    <t>b7cbc67480314c4992db4df3bf66f7cd</t>
   </si>
   <si>
     <t>df_rotary_dryer_Chaerhan</t>
   </si>
   <si>
-    <t>cf7c7c5a82664399ad7c9ca893c5b4a9</t>
+    <t>b0795fab05e94c43ab08227875950091</t>
   </si>
   <si>
     <t>df_rotary_dryer_East Taijinar</t>
   </si>
   <si>
-    <t>bff1fee646154f1f970f74c9ce183718</t>
+    <t>9088401b98ed4468969a48a23b3eab39</t>
   </si>
   <si>
     <t>df_rotary_dryer_Fenix</t>
   </si>
   <si>
-    <t>ef4f0a332eea49db915b6acf7d40b759</t>
+    <t>aa76c8e512f2487d93a39992fc11c378</t>
   </si>
   <si>
     <t>df_rotary_dryer_Kachi</t>
   </si>
   <si>
-    <t>72889ea5e62e4410a64da031f7ea6608</t>
+    <t>9356c8dc6cb548298507b02c9ae2d689</t>
   </si>
   <si>
     <t>df_rotary_dryer_Lakkor Tso</t>
   </si>
   <si>
-    <t>297450b0d3a84a009511e3575387bc82</t>
+    <t>11ae5d327f6648a09af931bee99de0d9</t>
   </si>
   <si>
     <t>df_rotary_dryer_Maricunga</t>
   </si>
   <si>
-    <t>d06fe64c845b49ccb6df9284bc76a713</t>
+    <t>fda909a10c944c05880971413e293ec9</t>
   </si>
   <si>
     <t>df_rotary_dryer_Pozuelos</t>
   </si>
   <si>
-    <t>c870d948024d4a6ca58daf631e258423</t>
+    <t>3dc6e915cb964b5694331a6bc37c7cf7</t>
   </si>
   <si>
     <t>df_rotary_dryer_Qinghai Yiliping</t>
   </si>
   <si>
-    <t>a9f62d68f5fc46a89a94eadf84e391b9</t>
+    <t>26766c9cccf04ef482eca6e7fb091bd0</t>
   </si>
   <si>
     <t>df_rotary_dryer_Sal de Vida</t>
   </si>
   <si>
-    <t>c5b034ddd0de457698a005e7e61416fa</t>
+    <t>e597d49a8eba4b588c8de2972670e375</t>
   </si>
   <si>
     <t>df_rotary_dryer_Sal de los Angeles</t>
   </si>
   <si>
-    <t>1a0e7fe5ad414a45a458b594ea74d7f3</t>
+    <t>fec1113458be4b7dbfe51e62d9346100</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar de Arizaro</t>
   </si>
   <si>
-    <t>b2e9a2e47c1f4a72b336f345d442b6e7</t>
+    <t>34fb2c22998943298c09a37ef3b9382d</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar de Atacama</t>
   </si>
   <si>
-    <t>74071979725343b9b2b258473e40b956</t>
+    <t>7bdbae8af92247578e4c191872b9dd00</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>a4356d69786646be87a22d0768fd3f03</t>
+    <t>968015d8cdf5413283f8c0fed95f5d75</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar de Centenario</t>
   </si>
   <si>
-    <t>8fd9ec77e0104eb7819691fe999b8969</t>
+    <t>79b0f4a0c2db44d389dbfd8344e19808</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar de Olaroz</t>
   </si>
   <si>
-    <t>7e9936daa35e423c9c4015cb1616be8f</t>
+    <t>17a643d47e5f4011988cfdd36546255a</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>9496df300a654c3882a8e493f5b7b144</t>
+    <t>3ec2243cbcd44b32867166f843ff446e</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar de Tolillar</t>
   </si>
   <si>
-    <t>ce05982e25bc4ade8abc196d58255d23</t>
+    <t>d7d8e3da0dd642a286b463688b57b8e6</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar de Uyuni</t>
   </si>
   <si>
-    <t>9152ef3cef4d4424888a70dc371795bc</t>
+    <t>78475d2714494a919ca37f8c10ab6ef0</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>d771bf7b156b4e7983ffd670352044a5</t>
+    <t>ff5abe0de42c437386664c78c9e52a51</t>
   </si>
   <si>
     <t>df_rotary_dryer_Salar del Rincon</t>
   </si>
   <si>
-    <t>cd4989f190f0425ba3d16453f67b600e</t>
+    <t>0bd6a11f87a6471ba703c82077e26fd1</t>
   </si>
   <si>
     <t>df_rotary_dryer_Silver Peak</t>
   </si>
   <si>
-    <t>986f28eb8be04850b3b32ef73e83c103</t>
+    <t>a9eab603330e407096bb59641d76daa6</t>
   </si>
   <si>
     <t>df_rotary_dryer_Tres Quebradas</t>
   </si>
   <si>
-    <t>a246c6c9fb0a4d7294f14dd28b714d89</t>
-  </si>
-  <si>
-    <t>6bea88d7f8964e31a3c6e95ccf1892a1</t>
+    <t>14b1478ef74b40f4972e79cfb4bc8bb6</t>
+  </si>
+  <si>
+    <t>7a45dcb9f2a24566949ed3264d776096</t>
   </si>
   <si>
     <t>df_rotary_dryer_Zhabuye</t>
   </si>
   <si>
-    <t>cc2d15b579a648188140ee0dc8f34e7e</t>
-  </si>
-  <si>
-    <t>ef2108ea390d4587992edfb6888c64f6</t>
+    <t>70b997feab38441ebb069ba7e34e2c60</t>
+  </si>
+  <si>
+    <t>a286f9dfa35a45e5af604646fcb0969b</t>
   </si>
   <si>
     <t>market for calcium chloride</t>
@@ -2866,10 +2866,10 @@
     <t>calcium chloride</t>
   </si>
   <si>
-    <t>2678ad3d15a9407381707e0beffaed45</t>
-  </si>
-  <si>
-    <t>8d91c15e52ff4f14a858ba186e9ba2d8</t>
+    <t>f6b85e93b4e747dd879c7a16d6c3f153</t>
+  </si>
+  <si>
+    <t>97e1c9d9d89b42459c31607b2b63622e</t>
   </si>
   <si>
     <t>transport, freight, lorry &gt;32 metric ton, EURO3</t>
@@ -2878,13 +2878,13 @@
     <t>ton kilometer</t>
   </si>
   <si>
-    <t>dd512cd2f7fd4620868ed3cd3a889051</t>
-  </si>
-  <si>
-    <t>f4a04df267104714a14b79a5e1c74715</t>
-  </si>
-  <si>
-    <t>9c25434f3dcf43bbad046a5df3a06283</t>
+    <t>b6a29c98a9f14986b8966a6c95217f02</t>
+  </si>
+  <si>
+    <t>774f024f3d87468ca694cc168eb22249</t>
+  </si>
+  <si>
+    <t>e46a5f9244754cc68962f4ce7b5e976a</t>
   </si>
   <si>
     <t>market for steam, in chemical industry</t>
@@ -2893,229 +2893,229 @@
     <t>steam, in chemical industry</t>
   </si>
   <si>
-    <t>c8a9251abc774fd690a221cc9f6ea04c</t>
+    <t>5010bdbfb4764be28dc3f902170e0b1c</t>
   </si>
   <si>
     <t>df_triple_evaporator_Pozuelos</t>
   </si>
   <si>
-    <t>df7a344e7ce546e19912ba174e88410b</t>
-  </si>
-  <si>
-    <t>5ce341db4ea84f6dac0338690a87902d</t>
+    <t>bc72669e2df949f188891f36738ecc1d</t>
+  </si>
+  <si>
+    <t>b3cef85566424d908dda412e8f499f47</t>
   </si>
   <si>
     <t>df_triple_evaporator_Salar de Arizaro</t>
   </si>
   <si>
-    <t>5dc195b8c6a64f0ba01357e7e5593a96</t>
-  </si>
-  <si>
-    <t>d57ee218e9ff478cb6cea6013997c41a</t>
-  </si>
-  <si>
-    <t>52926c0829b04d02ab1cca21e6d1778d</t>
+    <t>ff27d65bb7e34febbcbe8004bbeca081</t>
+  </si>
+  <si>
+    <t>6fb0d565fae44bfbb26fcf16dbe0e00b</t>
+  </si>
+  <si>
+    <t>d53fdf00983e4a17a4db16da6f785ec7</t>
   </si>
   <si>
     <t>df_triple_evaporator_Salar de Tolillar</t>
   </si>
   <si>
-    <t>1934ef42fc0b4bf8b6fe280891389f78</t>
-  </si>
-  <si>
-    <t>d1969496f688421796fe07ede36b4ea0</t>
-  </si>
-  <si>
-    <t>e6775f95219849f79e9e42bfc14849cf</t>
-  </si>
-  <si>
-    <t>2fae4942587045678312d626e6880ecf</t>
-  </si>
-  <si>
-    <t>b0714e4581fc4f6db8e55e14ba6713eb</t>
-  </si>
-  <si>
-    <t>96314d1aa138407e94cf89ec6b0cc684</t>
-  </si>
-  <si>
-    <t>47b5c63c2b9b444dbe3f5bff0fb59837</t>
-  </si>
-  <si>
-    <t>08ac53b896f24a35801a5ad91eabeb61</t>
-  </si>
-  <si>
-    <t>b7029aa250c047fe9b754d336deaad79</t>
-  </si>
-  <si>
-    <t>13c8059c902c4e14a930752a316ad6e4</t>
+    <t>3adf0b593dcf4745bdd2a19b9be2a0a3</t>
+  </si>
+  <si>
+    <t>bd95bd1bc7de43a984ab8e5301ee37b9</t>
+  </si>
+  <si>
+    <t>1c8842ec14e844aca9a1054f5895a5b4</t>
+  </si>
+  <si>
+    <t>9d4605a6eedc41ad857730274ecfb200</t>
+  </si>
+  <si>
+    <t>d53beb4253584c50bd5b9799e0d53a9d</t>
+  </si>
+  <si>
+    <t>0b213d88c34f4ca4921b4ed19f2810c6</t>
+  </si>
+  <si>
+    <t>76e89e8144714c658f806afcc35d76ce</t>
+  </si>
+  <si>
+    <t>823ad447907f4f419a6cb11492473a27</t>
+  </si>
+  <si>
+    <t>91f530d12490496c92c374691c4b1dd6</t>
+  </si>
+  <si>
+    <t>132e2987b8fa4bc998ce401d534bc08d</t>
   </si>
   <si>
     <t>df_washing_BG_Pozuelos</t>
   </si>
   <si>
-    <t>d3daf7e358ad4e5b98cdef148c9fdda3</t>
-  </si>
-  <si>
-    <t>b16629b46ce348ac8484c9ff648f8bcb</t>
+    <t>b0f0a6c515b345038f80dd9e3bf676ee</t>
+  </si>
+  <si>
+    <t>4f89eb8332de4445966d447e5a1f8a57</t>
   </si>
   <si>
     <t>df_washing_BG_Sal de Vida</t>
   </si>
   <si>
-    <t>3b241eb5daf54cad9038804dc28cdc15</t>
-  </si>
-  <si>
-    <t>038e89e8d2624fe38b3f366a6aa27538</t>
+    <t>9a07de3668494acf94a03b06e909ae8e</t>
+  </si>
+  <si>
+    <t>5241bba4f2e8447cbc3766e8e3779a2f</t>
   </si>
   <si>
     <t>df_washing_BG_Salar de Arizaro</t>
   </si>
   <si>
-    <t>d157c1640d3c4da59f1740f135c86362</t>
-  </si>
-  <si>
-    <t>3f56c3121b0e4256a65c38055eaa67f2</t>
-  </si>
-  <si>
-    <t>63479dae544a434e80660d432b57a06f</t>
-  </si>
-  <si>
-    <t>0ddb7d8a86004126a339f21d3c906c11</t>
-  </si>
-  <si>
-    <t>bad901d4b2594abe98b3b76f09430634</t>
+    <t>c8fbf3de480e4c998b2a3acd2b642e6e</t>
+  </si>
+  <si>
+    <t>950b7c291795438b9e0293a8d1c2fd01</t>
+  </si>
+  <si>
+    <t>9ba7d59f977d4547885d20c230bebbc6</t>
+  </si>
+  <si>
+    <t>c35ae405fa9e4abeaff995680e448774</t>
+  </si>
+  <si>
+    <t>b840ac8229954ed29bd692ad3a7bda81</t>
   </si>
   <si>
     <t>df_washing_BG_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>b87311f6f0184cb9ad3c13a659367915</t>
+    <t>3cbb772561a047279fa8ea1a1fc231e2</t>
   </si>
   <si>
     <t>df_washing_BG_Salar de Tolillar</t>
   </si>
   <si>
-    <t>962f30969a5d46a7b2bc16d19e929307</t>
-  </si>
-  <si>
-    <t>515db94f20d84f3ca3819873bfc4d240</t>
+    <t>0fd0bcd996494b2f89aa3482fd80a1cb</t>
+  </si>
+  <si>
+    <t>b24f4c42aaf740c2a6f541845d93c43c</t>
   </si>
   <si>
     <t>df_washing_BG_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>2d354b2e03234d4ea5d0220d35346783</t>
-  </si>
-  <si>
-    <t>22e7bb0878b54cd9ba213473bfaa61a4</t>
-  </si>
-  <si>
-    <t>e4194374722a4bada52b50f755ba4f77</t>
-  </si>
-  <si>
-    <t>a3909910c4b8487381d5e7e5efbd3c91</t>
-  </si>
-  <si>
-    <t>e29b0744ea934360b2dfcd5b5aa67131</t>
-  </si>
-  <si>
-    <t>56fccb3736f8443cb3c31e1f27831871</t>
-  </si>
-  <si>
-    <t>60d0d6b38ed344d7b102f6961509c2db</t>
-  </si>
-  <si>
-    <t>34572be9f7ac4e65952de1a60b43faa6</t>
-  </si>
-  <si>
-    <t>e01c491456f14d9b9e2846ca1ccb3a35</t>
-  </si>
-  <si>
-    <t>28b3e2ce7f344cabaf4ba75ac09cfd57</t>
-  </si>
-  <si>
-    <t>2fcef1ed13b148c68dc78c8c3d9b7f4c</t>
-  </si>
-  <si>
-    <t>66e78087f2144315ae4514cd877c4857</t>
+    <t>f08f89ab140d4da58fd6b4fe30226b61</t>
+  </si>
+  <si>
+    <t>3fda9feb435e466082b8d2c8397f654b</t>
+  </si>
+  <si>
+    <t>4374c56ee28844a7928b6b03fefc5103</t>
+  </si>
+  <si>
+    <t>85a8218811d6444ca47e978a1056e7e5</t>
+  </si>
+  <si>
+    <t>38bc1852bdb147e987d354ced4c25ae4</t>
+  </si>
+  <si>
+    <t>1008174e37fc40c0a614acc2574ef321</t>
+  </si>
+  <si>
+    <t>391ff1d6a87044408bc3636128cf6c3e</t>
+  </si>
+  <si>
+    <t>057e545cafd24fbd969b51a47d7d4cb8</t>
+  </si>
+  <si>
+    <t>115acaf3ef4f4b3cb0f640ab4296b9a4</t>
+  </si>
+  <si>
+    <t>0b29bbe464fe4ee9abf7468584ae5b86</t>
+  </si>
+  <si>
+    <t>56528db816134ef9af616981342decca</t>
+  </si>
+  <si>
+    <t>8aea5ee71dee459181bb98a52c1dff62</t>
   </si>
   <si>
     <t>df_washing_TG_Pozuelos</t>
   </si>
   <si>
-    <t>3a7adc5b1e364580adb504a70407d30f</t>
-  </si>
-  <si>
-    <t>420dcb4b526a4c7e8ff9b0dd31fb1160</t>
+    <t>6f1579fe83774dc7aa45683ad64844f7</t>
+  </si>
+  <si>
+    <t>226eb51f0deb41318d2b141d8f37faf3</t>
   </si>
   <si>
     <t>df_washing_TG_Sal de Vida</t>
   </si>
   <si>
-    <t>ec80b8aece234627ab8b5d2aa773e7de</t>
-  </si>
-  <si>
-    <t>5030f3e3969742829f907c3712260911</t>
+    <t>f976eb9922b1412cbd6aea5cc380aaf5</t>
+  </si>
+  <si>
+    <t>e6ae9f5fa5b34d5992278c0c22991e73</t>
   </si>
   <si>
     <t>df_washing_TG_Salar de Arizaro</t>
   </si>
   <si>
-    <t>cb4c6610c86349b68be7d7e9d54db045</t>
-  </si>
-  <si>
-    <t>67ebea0f78f74c2bbc373ce8ad77d800</t>
-  </si>
-  <si>
-    <t>8c66756dd05744b99d73cb73c1f0247b</t>
-  </si>
-  <si>
-    <t>b5f23f38085e4b0fa9586fe7943bda00</t>
-  </si>
-  <si>
-    <t>42d937ae67514c5b9055551ff484cb4a</t>
+    <t>6e63e9a2f2394247bb76f94fada3534f</t>
+  </si>
+  <si>
+    <t>67e109b3b62d4322af44c003053c4d47</t>
+  </si>
+  <si>
+    <t>2426636d12fe4cdf988eee9679e24588</t>
+  </si>
+  <si>
+    <t>5d6189558ef2450ba0b8ca560790d948</t>
+  </si>
+  <si>
+    <t>12d13b5fc3184762bf2bbbd08898547a</t>
   </si>
   <si>
     <t>df_washing_TG_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>ddac650b594b4277bb52b1a8e0d039ce</t>
+    <t>7b210e01fd92477281eda63f9145cf6f</t>
   </si>
   <si>
     <t>df_washing_TG_Salar de Tolillar</t>
   </si>
   <si>
-    <t>79346d872770402fab4ae1622b29b743</t>
-  </si>
-  <si>
-    <t>ae1488951d2e4226a1a5d72b2e21a452</t>
+    <t>e8ebb79c1f704fce9df4b5edba72a235</t>
+  </si>
+  <si>
+    <t>51e63645244f45fd9c6648c6e0db6702</t>
   </si>
   <si>
     <t>df_washing_TG_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>a7786becdfec4bf2aaa69db584ce0079</t>
-  </si>
-  <si>
-    <t>6221a1c3882e48618cb7bfc4e03d882b</t>
-  </si>
-  <si>
-    <t>5af387a3b65e40db926e86917cb43677</t>
-  </si>
-  <si>
-    <t>e98f3ff6a46b422993cf20a9ac11c674</t>
-  </si>
-  <si>
-    <t>336fd02559f14f9192ef271aa5e8d8e9</t>
-  </si>
-  <si>
-    <t>da8b5579910e4537a00db501812f1d3c</t>
+    <t>72011668b04c4097a7e1945acb1f212f</t>
+  </si>
+  <si>
+    <t>357a986f053b486cb6e28eb68f2ee859</t>
+  </si>
+  <si>
+    <t>ae038368116e4b348d212c0d1d158954</t>
+  </si>
+  <si>
+    <t>172f58d100e545e59ab4dfc5e6822270</t>
+  </si>
+  <si>
+    <t>769cd0f667b2463bb5f3d9b15df2c65f</t>
+  </si>
+  <si>
+    <t>95dce6f0db5840009c64caa08f2ceceb</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Chaerhan</t>
   </si>
   <si>
-    <t>5a2bb09405ce4eee9b569ca3de2281a8</t>
+    <t>d499790a2ad449f4bc1c0bb28acd03bc</t>
   </si>
   <si>
     <t>database</t>
@@ -3142,337 +3142,337 @@
     <t>heat production, at heat pump 30kW, allocation exergy, East Taijinar</t>
   </si>
   <si>
-    <t>ef53fbf1169c4582bb7e4707a88dca05</t>
+    <t>259b399bd97c471cb99ac6faea8136b1</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Fenix</t>
   </si>
   <si>
-    <t>18ab38a755c1447bb30e992c4a99102f</t>
+    <t>fb77e71e84a142049fb798a5597f11c4</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Kachi</t>
   </si>
   <si>
-    <t>f46586c7946745ec967b125965122a6d</t>
+    <t>996b717bfc7d426b8bffbfc5e62b60a3</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Lakkor Tso</t>
   </si>
   <si>
-    <t>d00719a8dcc54000ad667283fac12e93</t>
+    <t>59842d2b88784ad199d917256b0f1ac8</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Maricunga</t>
   </si>
   <si>
-    <t>7e0660d3a8004f50b9033baf5f749892</t>
+    <t>361be9061fd04e6f83800706dc3950ac</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Pozuelos</t>
   </si>
   <si>
-    <t>50a34dc1c1354a07a0028db910091e66</t>
+    <t>8aaccbfde8b14e2bbb7657eecd0a582c</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Qinghai Yiliping</t>
   </si>
   <si>
-    <t>17c06fc550034c9bb234ed24964db5e7</t>
+    <t>81f7d866a8f5410c828c915811d04de8</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Sal de Vida</t>
   </si>
   <si>
-    <t>c06a7755ae5549cabf991ce1d77c2579</t>
+    <t>0f1c4eed38b241fa91d5d608e308cec6</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Sal de los Angeles</t>
   </si>
   <si>
-    <t>e2a55cef654c47eeab31c30c700465f4</t>
+    <t>bf19e636901c4f0eb0976ec498adf2ea</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar de Arizaro</t>
   </si>
   <si>
-    <t>cd87f252a1c848309bed0164330b53a0</t>
+    <t>84f9c5ca30a54938b26f8d5b13f54fb5</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar de Atacama</t>
   </si>
   <si>
-    <t>ed34010217924cc6bf232c03889b68cd</t>
+    <t>3d8125d185dc4ebfac68915a605080f7</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>b7ffa77556f447bab5d5e4a24fddf505</t>
+    <t>255113d331c9436aaca62410f895070d</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar de Centenario</t>
   </si>
   <si>
-    <t>39f4e32849bf4da899d9b0e2a431779a</t>
+    <t>6aca51a5b1a048b796b98f6d2ce4d2a1</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar de Olaroz</t>
   </si>
   <si>
-    <t>39914e9b20e549d6b18235c37b1337be</t>
+    <t>53d9b2715a2f4dea924aac739899e331</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>e46cb3020d04473595c352a6be74ef88</t>
+    <t>434f9e89509a4ef4b6ca5efcf686679b</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar de Tolillar</t>
   </si>
   <si>
-    <t>99be6d74e437448face6aa69a2ae49b5</t>
+    <t>70dfc531730343c18cf8f2e29cba57f6</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar de Uyuni</t>
   </si>
   <si>
-    <t>a0ad2875b1d44500bd63f4721b23bead</t>
+    <t>a88c129ee34d474b967f69eef1b56064</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>80e33164d76544a7bdf54dc6306793d6</t>
+    <t>d2a4f6c153094d85bd3a373bfe485c2e</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Salar del Rincon</t>
   </si>
   <si>
-    <t>633aa03289464613966012777345aada</t>
+    <t>712926350ea04ecfa4df490277238af7</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Silver Peak</t>
   </si>
   <si>
-    <t>7620f54c19f44f2aa9970c47f3af2fbb</t>
+    <t>634be80694c5414bbef5d753926add0f</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Tres Quebradas</t>
   </si>
   <si>
-    <t>e5ce9fb6128648fe84b5ae7049d41e70</t>
+    <t>a6ec70b88d634f52b022283232f82644</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Upper Rhine Graben</t>
   </si>
   <si>
-    <t>ed137b055c314a99b7fe7ff16df220a3</t>
+    <t>1afe5235b8354dafa40332d7d09c3e10</t>
   </si>
   <si>
     <t>heat production, at heat pump 30kW, allocation exergy, Zhabuye</t>
   </si>
   <si>
-    <t>b8656311eab2420194f06aa2df5b7bae</t>
+    <t>4bada575b0ff49d99031bcf1b3c60757</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Chaerhan</t>
   </si>
   <si>
-    <t>1808b6b30bef4b9bb2712a5c53275c43</t>
+    <t>501bb177844a4f709474775b9ed91ac7</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, East Taijinar</t>
   </si>
   <si>
-    <t>6c946bc1611845be8932d75e6de4b688</t>
+    <t>fcc8e7a1e1e7436488b29448676d84b6</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Fenix</t>
   </si>
   <si>
-    <t>54e7fab3ccd44eabbcf1d9735f780273</t>
+    <t>25e41f7cb371465ebb0ff97540bd5ee9</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Kachi</t>
   </si>
   <si>
-    <t>00a0f74ee3624f968b164416e9046558</t>
+    <t>eee3ccf3e9184cd48d77ce477a2ce302</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Lakkor Tso</t>
   </si>
   <si>
-    <t>eb16fef73c084f15919dbfcb050a9bcd</t>
+    <t>abe1caefdce64dc2ba574020222e580c</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Maricunga</t>
   </si>
   <si>
-    <t>865520064f0d492b8c5f5e693778c253</t>
+    <t>eb5a59d40fb446c4bffc157d29d98ca9</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Pozuelos</t>
   </si>
   <si>
-    <t>5a830fb12daa4d978690ace365a79862</t>
+    <t>2a88c89dd1a94e74971e51edf6cc1a9b</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Qinghai Yiliping</t>
   </si>
   <si>
-    <t>965361d5f6434dde89d5057865cc6590</t>
+    <t>c6172957161f48f0bd0a3914036d2e43</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Sal de Vida</t>
   </si>
   <si>
-    <t>817161df7a694f4a8a12e32bff4db0be</t>
+    <t>25c9b7a73793460fb019a4d4c752f7c0</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Sal de los Angeles</t>
   </si>
   <si>
-    <t>419bee3f289d46e39fc583fbe53440d6</t>
+    <t>0ab56a26fb2948e19b084a8edddaf6ba</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar de Arizaro</t>
   </si>
   <si>
-    <t>a835cd6bd8b04355b4a3b838ca4363e7</t>
+    <t>fd2582afee774e8bb96e272c5edb5fc0</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar de Atacama</t>
   </si>
   <si>
-    <t>8eafc25578c64305980fbbb1bcf6ba20</t>
+    <t>c75a0aa415d9433ab9c35f0f0eb13f51</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar de Cauchari-Olaroz</t>
   </si>
   <si>
-    <t>c71159a3d0fc49e781da6377c9b3acdd</t>
+    <t>c267a3a40e6d47b09ec8ecceece7ee68</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar de Centenario</t>
   </si>
   <si>
-    <t>4e1bd215b46445c0a4daa44529424dff</t>
+    <t>fd7b0871691e43ed844d13c2ad0b91b1</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar de Olaroz</t>
   </si>
   <si>
-    <t>e99685964d1c474e867c7f803568ff11</t>
+    <t>a2350b671ec940e6a5b4f1ab8350085a</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>ed2fd59a1ffe4eb58263da409b47a764</t>
+    <t>0a50d40788fe47468aa07245a36ab58f</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar de Tolillar</t>
   </si>
   <si>
-    <t>da3879a94be6407298346650e5c4c224</t>
+    <t>fe6493285ddf40ec8f049c004db0f99e</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar de Uyuni</t>
   </si>
   <si>
-    <t>ee1e050f4ec34f6dbeacaba9dbaa00c3</t>
+    <t>ad05a991a10e4253befa9e68956020ea</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>8c9d5eea18454224816be6af2e6044b0</t>
-  </si>
-  <si>
-    <t>0076d910a69a442d86afd4f1bc981e41</t>
+    <t>2dca35db848f482b895aa34dfb6668b4</t>
+  </si>
+  <si>
+    <t>76d78bfc0cd9437da373d3ac8ce22db7</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Silver Peak</t>
   </si>
   <si>
-    <t>9e04476cceee4ec19f0da13d9aef032f</t>
+    <t>cf9064c415574281866a969826d5488e</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Tres Quebradas</t>
   </si>
   <si>
-    <t>de37128425a94dd0b5f9de5a4e82d16c</t>
+    <t>707d8b607e634428adefd9f02096d895</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Upper Rhine Graben</t>
   </si>
   <si>
-    <t>bf790074beb9437693470fe8f5242a9e</t>
+    <t>99d161474c484d44a1590b4528f5a741</t>
   </si>
   <si>
     <t>heat production, industrial electric boiler, Zhabuye</t>
   </si>
   <si>
-    <t>87e35023b4124f3ca2cbe2ab910ec417</t>
-  </si>
-  <si>
-    <t>d1fd1dece0f4420ebecadf5c2cac5e67</t>
+    <t>5209ca6ecbbf4710aa92513664a23e57</t>
+  </si>
+  <si>
+    <t>1fb52214063349339a5f838feb7643f8</t>
   </si>
   <si>
     <t>waste_liquid_Ari_Salar de Arizaro</t>
   </si>
   <si>
-    <t>f97ccfea06604655b103f43b19a8590a</t>
+    <t>016391281ec741dd9fb37da9d70bd15f</t>
   </si>
   <si>
     <t>waste_liquid_Ari</t>
   </si>
   <si>
-    <t>e072fe64d4cd49cabde8c86568d1f16e</t>
-  </si>
-  <si>
-    <t>94c2c99d08cc448fb67d4aa31dc36e81</t>
-  </si>
-  <si>
-    <t>f02e2421ec4c46b29fcf78062fdc797a</t>
-  </si>
-  <si>
-    <t>a35099e4f2e44a27a811de4ad91bbbfa</t>
-  </si>
-  <si>
-    <t>98c2f78a9ec5456c8610d47ba6dc25f1</t>
-  </si>
-  <si>
-    <t>be8aef76af404018a237bcd147ab35ba</t>
+    <t>85571ee0febc4c31ac51e90607596e98</t>
+  </si>
+  <si>
+    <t>2c26e1bf5c474e6a99b29b2f908206f3</t>
+  </si>
+  <si>
+    <t>d0f5de6b9a0e4bf6a8742f8fc1552461</t>
+  </si>
+  <si>
+    <t>1ff9c6d898a5462aaf4c3e0990639d0c</t>
+  </si>
+  <si>
+    <t>0670c60966dd4488862a61460daae602</t>
+  </si>
+  <si>
+    <t>7418bf505b774282b8dd5fdf5efec989</t>
   </si>
   <si>
     <t>waste_liquid_Hom_Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>043704b3f82d4818ae58f1abe4812359</t>
+    <t>c53aee13b7524b398374beadfad39616</t>
   </si>
   <si>
     <t>waste_liquid_Hom</t>
   </si>
   <si>
-    <t>c603a7134c824589b6ef958e1600a56d</t>
-  </si>
-  <si>
-    <t>51076585f5a74295814b486c76bca561</t>
-  </si>
-  <si>
-    <t>8dbcbaf7a22d4b33b2222633b0b64807</t>
-  </si>
-  <si>
-    <t>67ad833a45e942e7be1ec820042f8ced</t>
+    <t>803dfdd5619143cbb37e01ccf00a9f75</t>
+  </si>
+  <si>
+    <t>1e99efbc818d4a77b3e208672a8ed8e9</t>
+  </si>
+  <si>
+    <t>dd36ee23736d47f99c17ec2a79a50581</t>
+  </si>
+  <si>
+    <t>1f9858610ff1465b90145292938b89bf</t>
   </si>
   <si>
     <t>waste_liquid_Pas_Salar de Pastos Grandes</t>
   </si>
   <si>
-    <t>f2e9efe551e04d43a174429d38291b0e</t>
+    <t>03beea7081124116b2057d28bc9164b5</t>
   </si>
   <si>
     <t>waste_liquid_Pas</t>
@@ -3481,46 +3481,46 @@
     <t>waste_liquid_Poz_Pozuelos</t>
   </si>
   <si>
-    <t>4bf6c02558ff4b099361bc626f90f7dc</t>
+    <t>f71ffe68dd9a42549fed496a3ec777f7</t>
   </si>
   <si>
     <t>waste_liquid_Poz</t>
   </si>
   <si>
-    <t>71e627c6e69349a1b504920876d48802</t>
-  </si>
-  <si>
-    <t>d2065ce352a142bc9fa34aabe7308d7d</t>
+    <t>b50b0a242ca94dba98e42c72b6413b97</t>
+  </si>
+  <si>
+    <t>ba44454c08f745c59af24a062d25f292</t>
   </si>
   <si>
     <t>waste_liquid_Tol_Salar de Tolillar</t>
   </si>
   <si>
-    <t>17c5bedaebe94864877eb5c9c4dad7ea</t>
+    <t>c701e1c41fe64ace913099ad925e4f1d</t>
   </si>
   <si>
     <t>waste_liquid_Tol</t>
   </si>
   <si>
-    <t>273cc0da8f9949a4aa9c6262f7e510d7</t>
-  </si>
-  <si>
-    <t>c1378fcdfa284b74b2e6a3309a52f106</t>
+    <t>80ea2ebdade44ca6a015d6242aaed6dd</t>
+  </si>
+  <si>
+    <t>26191f12f22a4fa5b8e3d9cd4bef6fb9</t>
   </si>
   <si>
     <t>waste_liquid_Vid_Sal de Vida</t>
   </si>
   <si>
-    <t>26b683ebed2f44cc840bef7ec30b633c</t>
+    <t>620d199bbd164e0ba8f374889bb90e71</t>
   </si>
   <si>
     <t>waste_liquid_Vid</t>
   </si>
   <si>
-    <t>eacdb4466a6940758abda5c1c61bffcb</t>
-  </si>
-  <si>
-    <t>6da73096036f48af88c69e7f48494873</t>
+    <t>1787d599f0af4423b75da318638eb0da</t>
+  </si>
+  <si>
+    <t>ea04f86056e54d9692a83556a753b83f</t>
   </si>
 </sst>
 </file>
